--- a/argus/kship/models/096350_model.xlsx
+++ b/argus/kship/models/096350_model.xlsx
@@ -648,61 +648,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 181938억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 181941억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 192222억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 192336억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 198074억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 198297억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 199623억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 200366억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 198774억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 199616억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 196986억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 197819억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 193705억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 194529억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 189964억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 190369억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 185574억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 185978억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 179406억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 179810억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1845,61 +1845,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 181938억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 181941억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 192222억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 192336억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 198074억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 198297억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 199623억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 200366억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 198774억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 199616억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 196986억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 197819억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 193705억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 194529억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 189964억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 190369억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 185574억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 185978억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 179406억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 179810억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -6689,33 +6689,33 @@
         <v>0.200542</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.37528</v>
+        <v>0.376068</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.03028</v>
+        <v>0.031409</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.153401</v>
+        <v>0.15769</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.092542</v>
+        <v>0.09715500000000001</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.024751</v>
+        <v>0.028499</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.022064</v>
+        <v>-0.018982</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.048386</v>
+        <v>-0.049899</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.066439</v>
+        <v>-0.068328</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.089229</v>
+        <v>-0.09103899999999999</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6835,39 +6835,39 @@
         <v>0.129685</v>
       </c>
       <c r="AD22" s="24" t="n">
-        <v>0.129689</v>
+        <v>0.129656</v>
       </c>
       <c r="AE22" s="25">
         <f>IFERROR(subQ!AE8/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.129688</v>
+        <v>0.129683</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.129688</v>
+        <v>0.129665</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.129677</v>
+        <v>0.129663</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.129671</v>
+        <v>0.129681</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.129671</v>
+        <v>0.12968</v>
       </c>
       <c r="AL22" s="24" t="n">
+        <v>0.129688</v>
+      </c>
+      <c r="AM22" s="24" t="n">
         <v>0.129673</v>
       </c>
-      <c r="AM22" s="24" t="n">
-        <v>0.129671</v>
-      </c>
       <c r="AN22" s="24" t="n">
-        <v>0.129663</v>
+        <v>0.12968</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6997,32 +6997,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.001233</v>
+        <v>0.001232</v>
       </c>
       <c r="AG23" s="24" t="n">
+        <v>0.001235</v>
+      </c>
+      <c r="AH23" s="24" t="n">
         <v>0.001239</v>
       </c>
-      <c r="AH23" s="24" t="n">
-        <v>0.0012</v>
-      </c>
       <c r="AI23" s="24" t="n">
-        <v>0.001238</v>
+        <v>0.001232</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.001214</v>
+        <v>0.001209</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.001206</v>
+        <v>0.001203</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.001238</v>
+        <v>0.001235</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.001227</v>
+        <v>0.001225</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7980,7 +7980,7 @@
         <v>-0.003546</v>
       </c>
       <c r="AL30" s="24" t="n">
-        <v>-0.007092</v>
+        <v>-0.003546</v>
       </c>
       <c r="AM30" s="24" t="n">
         <v>-0.007067</v>
@@ -8223,26 +8223,26 @@
         <v>-0.01</v>
       </c>
       <c r="AG32" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AH32" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AI32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AL32" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AM32" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AN32" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO32" s="30" t="n"/>
     </row>
@@ -8351,26 +8351,26 @@
         <v>0</v>
       </c>
       <c r="AG33" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AI33" s="29" t="n">
         <v>-0.01</v>
-      </c>
-      <c r="AH33" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" s="29" t="n">
-        <v>0</v>
       </c>
       <c r="AJ33" s="30" t="n"/>
       <c r="AK33" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AL33" s="29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AM33" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AN33" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AM33" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" s="29" t="n">
-        <v>-0</v>
       </c>
       <c r="AO33" s="30" t="n"/>
     </row>
@@ -8620,10 +8620,10 @@
         <v>-0.005563</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>-0.005524</v>
+        <v>-0.005594</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>-0.005695</v>
+        <v>-0.005625</v>
       </c>
       <c r="AN35" s="24" t="n">
         <v>-0.005799</v>
@@ -8741,20 +8741,20 @@
         <v>0.004747</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.004901</v>
+        <v>0.00496</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
         <v>0.004701</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.004679</v>
+        <v>0.00462</v>
       </c>
       <c r="AM36" s="24" t="n">
         <v>0.004657</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.004752</v>
+        <v>0.00481</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9799,32 +9799,32 @@
         <v/>
       </c>
       <c r="AF45" s="24" t="n">
-        <v>0.001233</v>
+        <v>0.001232</v>
       </c>
       <c r="AG45" s="24" t="n">
+        <v>0.001235</v>
+      </c>
+      <c r="AH45" s="24" t="n">
         <v>0.001239</v>
       </c>
-      <c r="AH45" s="24" t="n">
-        <v>0.0012</v>
-      </c>
       <c r="AI45" s="24" t="n">
-        <v>0.001238</v>
+        <v>0.001232</v>
       </c>
       <c r="AJ45" s="25">
         <f>IFERROR(subQ!AJ36/subQ!AJ35,"")</f>
         <v/>
       </c>
       <c r="AK45" s="24" t="n">
-        <v>0.001214</v>
+        <v>0.001209</v>
       </c>
       <c r="AL45" s="24" t="n">
-        <v>0.001206</v>
+        <v>0.001203</v>
       </c>
       <c r="AM45" s="24" t="n">
-        <v>0.001238</v>
+        <v>0.001235</v>
       </c>
       <c r="AN45" s="24" t="n">
-        <v>0.001227</v>
+        <v>0.001225</v>
       </c>
       <c r="AO45" s="25">
         <f>IFERROR(subQ!AO36/subQ!AO35,"")</f>

--- a/argus/kship/models/096350_model.xlsx
+++ b/argus/kship/models/096350_model.xlsx
@@ -654,55 +654,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 192336억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 193175억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 198297억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 202273억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 200366억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 210912억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 199616억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 220975억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 197819억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 233879억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 194529억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 247938억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 190369억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 262590억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 185978억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 277323억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 179810억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 289469억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1851,55 +1851,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 192336억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 193175억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 198297억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 202273억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 200366억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 210912억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 199616억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 220975억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 197819억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 233879억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 194529억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 247938억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 190369억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 262590억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 185978억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 277323억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 179810억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 289469억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4510,7 +4510,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 37.4, "op_wape_pct": 99.6, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 109.34, "rev_act": 171.56, "op_pred": 0.07, "op_act": 11.72}, {"q": "2025Q4", "rev_pred": 149.49, "rev_act": 177.73, "op_pred": 0.09, "op_act": 1.71}, {"q": "2026Q1", "rev_pred": 87.38, "rev_act": 212.48, "op_pred": 0.05, "op_act": 14.82}, {"q": "2026Q2", "rev_pred": 123.68, "rev_act": 188.86, "op_pred": 0.08, "op_act": -1.36}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 37.4, "op_wape_pct": 99.6, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": {"wape_link": null, "wape_trend": null, "adopted": false, "note": "유의성 조건 미달 → OOS 비교 전 기각"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 109.34, "rev_act": 171.56, "op_pred": 0.07, "op_act": 11.72}, {"q": "2025Q4", "rev_pred": 149.49, "rev_act": 177.73, "op_pred": 0.09, "op_act": 1.71}, {"q": "2026Q1", "rev_pred": 87.38, "rev_act": 212.48, "op_pred": 0.05, "op_act": 14.82}, {"q": "2026Q2", "rev_pred": 123.68, "rev_act": 188.86, "op_pred": 0.08, "op_act": -1.36}]}</t>
         </is>
       </c>
     </row>
@@ -6689,33 +6689,33 @@
         <v>0.200542</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.376068</v>
+        <v>0.382088</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.031409</v>
+        <v>0.052117</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.15769</v>
+        <v>0.218635</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.09715500000000001</v>
+        <v>0.214556</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.028499</v>
+        <v>0.210715</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.018982</v>
+        <v>0.225766</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.049899</v>
+        <v>0.245014</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.068328</v>
+        <v>0.255007</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.09103899999999999</v>
+        <v>0.23766</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6835,39 +6835,39 @@
         <v>0.129685</v>
       </c>
       <c r="AD22" s="24" t="n">
-        <v>0.129656</v>
+        <v>0.129661</v>
       </c>
       <c r="AE22" s="25">
         <f>IFERROR(subQ!AE8/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.129683</v>
+        <v>0.12968</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.129665</v>
+        <v>0.129655</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.129663</v>
+        <v>0.129682</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.129681</v>
+        <v>0.129657</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.12968</v>
+        <v>0.129662</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.129688</v>
+        <v>0.129685</v>
       </c>
       <c r="AM22" s="24" t="n">
+        <v>0.129674</v>
+      </c>
+      <c r="AN22" s="24" t="n">
         <v>0.129673</v>
-      </c>
-      <c r="AN22" s="24" t="n">
-        <v>0.12968</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6990,39 +6990,39 @@
         <v>0.001214</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.001227</v>
+        <v>0.001221</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.001232</v>
+        <v>0.001208</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.001235</v>
+        <v>0.001217</v>
       </c>
       <c r="AH23" s="24" t="n">
         <v>0.001239</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.001232</v>
+        <v>0.00121</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.001209</v>
+        <v>0.001204</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.001203</v>
+        <v>0.001221</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.001235</v>
+        <v>0.00121</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.001225</v>
+        <v>0.001223</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7296,7 +7296,7 @@
         <v>0.77</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7574,7 +7574,7 @@
         <v>0.222222</v>
       </c>
       <c r="AD27" s="24" t="n">
-        <v>0.221154</v>
+        <v>0.219048</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE14/subQ!AE13,"")</f>
@@ -7584,29 +7584,29 @@
         <v>0.215686</v>
       </c>
       <c r="AG27" s="24" t="n">
-        <v>0.215686</v>
+        <v>0.223301</v>
       </c>
       <c r="AH27" s="24" t="n">
-        <v>0.223301</v>
+        <v>0.216981</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.214953</v>
+        <v>0.223214</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.223301</v>
+        <v>0.218182</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.215686</v>
+        <v>0.223214</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.223301</v>
+        <v>0.215517</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.219048</v>
+        <v>0.219512</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -7970,23 +7970,23 @@
       <c r="AF30" s="31" t="n"/>
       <c r="AG30" s="31" t="n"/>
       <c r="AH30" s="24" t="n">
-        <v>0.010714</v>
+        <v>0.021429</v>
       </c>
       <c r="AI30" s="24" t="n">
-        <v>0.003509</v>
+        <v>0.021053</v>
       </c>
       <c r="AJ30" s="25" t="n"/>
       <c r="AK30" s="24" t="n">
-        <v>-0.003546</v>
+        <v>0.024823</v>
       </c>
       <c r="AL30" s="24" t="n">
-        <v>-0.003546</v>
+        <v>0.024735</v>
       </c>
       <c r="AM30" s="24" t="n">
-        <v>-0.007067</v>
+        <v>0.024476</v>
       </c>
       <c r="AN30" s="24" t="n">
-        <v>-0.01049</v>
+        <v>0.030928</v>
       </c>
       <c r="AO30" s="25" t="n"/>
     </row>
@@ -8216,20 +8216,20 @@
         <v>0.0033</v>
       </c>
       <c r="AD32" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AE32" s="30" t="n"/>
       <c r="AF32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AG32" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AH32" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AI32" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
@@ -8344,7 +8344,7 @@
         <v>0.0007</v>
       </c>
       <c r="AD33" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AE33" s="30" t="n"/>
       <c r="AF33" s="29" t="n">
@@ -8357,17 +8357,17 @@
         <v>0.01</v>
       </c>
       <c r="AI33" s="29" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AJ33" s="30" t="n"/>
       <c r="AK33" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AL33" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AM33" s="29" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AN33" s="29" t="n">
         <v>0</v>
@@ -8607,26 +8607,26 @@
         <v>-0.005373</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>-0.005402</v>
+        <v>-0.005539</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>-0.005569</v>
+        <v>-0.005707</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>-0.005738</v>
+        <v>-0.006017</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>-0.005563</v>
+        <v>-0.005983</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>-0.005594</v>
+        <v>-0.006089</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>-0.005625</v>
+        <v>-0.006338</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>-0.005799</v>
+        <v>-0.006804</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8732,29 +8732,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.004732</v>
+        <v>0.004792</v>
       </c>
       <c r="AG36" s="24" t="n">
         <v>0.004769</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.004747</v>
+        <v>0.004924</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.00496</v>
+        <v>0.005195</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.004701</v>
+        <v>0.005051</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.00462</v>
+        <v>0.005084</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.004657</v>
+        <v>0.005233</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.00481</v>
+        <v>0.005553</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9384,21 +9384,21 @@
         <v>-0.363066</v>
       </c>
       <c r="AH42" s="24" t="n">
-        <v>-0.08988599999999999</v>
+        <v>-0.099978</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>1.224671</v>
+        <v>1.175751</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="31" t="n"/>
       <c r="AL42" s="24" t="n">
-        <v>0</v>
+        <v>-0.06317200000000001</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>0</v>
+        <v>-0.072171</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>0</v>
+        <v>-0.08998399999999999</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -9517,7 +9517,7 @@
         <v>-0.009523999999999999</v>
       </c>
       <c r="AN43" s="24" t="n">
-        <v>-0.009523999999999999</v>
+        <v>-0.014286</v>
       </c>
       <c r="AO43" s="25" t="n"/>
     </row>
@@ -9792,39 +9792,39 @@
         <v>0.001214</v>
       </c>
       <c r="AD45" s="24" t="n">
-        <v>0.001227</v>
+        <v>0.001221</v>
       </c>
       <c r="AE45" s="25">
         <f>IFERROR(subQ!AE36/subQ!AE35,"")</f>
         <v/>
       </c>
       <c r="AF45" s="24" t="n">
-        <v>0.001232</v>
+        <v>0.001208</v>
       </c>
       <c r="AG45" s="24" t="n">
-        <v>0.001235</v>
+        <v>0.001217</v>
       </c>
       <c r="AH45" s="24" t="n">
         <v>0.001239</v>
       </c>
       <c r="AI45" s="24" t="n">
-        <v>0.001232</v>
+        <v>0.00121</v>
       </c>
       <c r="AJ45" s="25">
         <f>IFERROR(subQ!AJ36/subQ!AJ35,"")</f>
         <v/>
       </c>
       <c r="AK45" s="24" t="n">
-        <v>0.001209</v>
+        <v>0.001204</v>
       </c>
       <c r="AL45" s="24" t="n">
-        <v>0.001203</v>
+        <v>0.001221</v>
       </c>
       <c r="AM45" s="24" t="n">
-        <v>0.001235</v>
+        <v>0.00121</v>
       </c>
       <c r="AN45" s="24" t="n">
-        <v>0.001225</v>
+        <v>0.001223</v>
       </c>
       <c r="AO45" s="25">
         <f>IFERROR(subQ!AO36/subQ!AO35,"")</f>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19109,7 +19109,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29728,7 +29728,7 @@
         <v>2.82</v>
       </c>
       <c r="AG18" s="20" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AH18" s="20">
         <f>IFERROR(AC18*(1+변수!AH30),"")</f>
@@ -32031,7 +32031,7 @@
         <v/>
       </c>
       <c r="AK33" s="20" t="n">
-        <v>211.01</v>
+        <v>201.94</v>
       </c>
       <c r="AL33" s="20">
         <f>IFERROR(AG33*(1+변수!AL42),"")</f>
@@ -40555,7 +40555,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>72.93000000000001</v>
+        <v>72.87</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/096350_model.xlsx
+++ b/argus/kship/models/096350_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 190606억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 190590억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 197951억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 197916억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 204818억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 204765억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 213897억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 213826억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 226773억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 226700억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 240817억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 240747억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 255473억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 255408억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 270212억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 270150억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 282374억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 282318억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 190606억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 190590억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 197951억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 197916억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 204818억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 204765억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 213897억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 213826억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 226773억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 226700억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 240817억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 240747억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 255473억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255408억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 270212억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 270150억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 282374억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 282318억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4439,7 +4439,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5667,35 +5667,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5786,35 +5786,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5905,35 +5905,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6024,35 +6024,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6143,35 +6143,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6278,7 +6278,7 @@
         <v>1859</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1901</v>
+        <v>1890</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6369,7 +6369,7 @@
         <v>2345</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>1928</v>
+        <v>1932</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6551,7 +6551,7 @@
         <v>1800.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1885.5</v>
+        <v>1887</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6706,33 +6706,33 @@
         <v>0.195237238</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.363689304</v>
+        <v>0.363576774</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.029620715</v>
+        <v>0.029432459</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.18342318</v>
+        <v>0.183105482</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.180882712</v>
+        <v>0.180492563</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.189751207</v>
+        <v>0.189478028</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.216574485</v>
+        <v>0.216431217</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.247293065</v>
+        <v>0.247314715</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.263277443</v>
+        <v>0.263405767</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245179637</v>
+        <v>0.245325563</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7017,39 +7017,39 @@
         <v>0.001219215</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.001237777</v>
+        <v>0.001237879</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.001234173</v>
+        <v>0.001234399</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.001208054</v>
+        <v>0.001208378</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.001238953</v>
+        <v>0.001239362</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.001213761</v>
+        <v>0.00121414</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.00120233</v>
+        <v>0.001202691</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.001219643</v>
+        <v>0.00121995</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.001209585</v>
+        <v>0.001209862</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.001225422</v>
+        <v>0.001225661</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8377,33 +8377,33 @@
         <v>0.003124085</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-6.598899999999999e-05</v>
+        <v>-6.6024e-05</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.000104536</v>
+        <v>0.000104602</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.000107326</v>
+        <v>0.000107236</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.01007653</v>
+        <v>0.010076417</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.009987784</v>
+        <v>-0.009987769000000001</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.000115628</v>
+        <v>0.000115493</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>1.7467e-05</v>
+        <v>1.7653e-05</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-8.036499999999999e-05</v>
+        <v>-8.0324e-05</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.000111104</v>
+        <v>-0.000111085</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8505,33 +8505,33 @@
         <v>0.000524085</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-6.598899999999999e-05</v>
+        <v>-6.6024e-05</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.010104536</v>
+        <v>0.010104602</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.009892674000000001</v>
+        <v>-0.009892764</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.01007653</v>
+        <v>0.010076417</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>1.2216e-05</v>
+        <v>1.2231e-05</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.009884372000000001</v>
+        <v>-0.009884507000000001</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>1.7467e-05</v>
+        <v>1.7653e-05</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-8.036499999999999e-05</v>
+        <v>-8.0324e-05</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.000111104</v>
+        <v>0.009888915</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>1901</v>
+        <v>1890</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1296700455502916</v>
+        <v>0.1296720264082633</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.01342097498615888</v>
+        <v>0.01342097498616116</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19920,7 +19920,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34862,7 +34862,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42486,7 +42486,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="33">
@@ -42520,7 +42520,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>110.61</v>
+        <v>110.26</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/096350_model.xlsx
+++ b/argus/kship/models/096350_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 190590억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 190576억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 197916억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 197880억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 204765억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 204706억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 213826억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 213745억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 226700억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 226612억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 240747억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 240663억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 255408억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 255328억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 270150억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 270076억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 282318억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 282250억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 190590억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 190576억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 197916억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 197880억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 204765억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 204706억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 213826억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 213745억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 226700억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 226612억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 240747억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 240663억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 255408억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255328억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 270150억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 270076억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 282318억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 282250억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4439,7 +4439,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5667,35 +5667,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5786,35 +5786,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5905,35 +5905,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6024,35 +6024,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6143,35 +6143,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6278,7 +6278,7 @@
         <v>1859</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1890</v>
+        <v>1909</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6551,7 +6551,7 @@
         <v>1800.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1887</v>
+        <v>1894.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6706,33 +6706,33 @@
         <v>0.195237238</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.363576774</v>
+        <v>0.363464245</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.029432459</v>
+        <v>0.029244203</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.183105482</v>
+        <v>0.182787785</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.180492563</v>
+        <v>0.180053645</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.189478028</v>
+        <v>0.189122271</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.216431217</v>
+        <v>0.216242169</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.247314715</v>
+        <v>0.247246844</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.263405767</v>
+        <v>0.26350374</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245325563</v>
+        <v>0.24552332</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7017,39 +7017,39 @@
         <v>0.001219215</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.001237879</v>
+        <v>0.001237981</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.001234399</v>
+        <v>0.001234624</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.001208378</v>
+        <v>0.001208703</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.001239362</v>
+        <v>0.001239823</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.00121414</v>
+        <v>0.001214603</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.001202691</v>
+        <v>0.001203098</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.00121995</v>
+        <v>0.001220344</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.001209862</v>
+        <v>0.001210218</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.001225661</v>
+        <v>0.001225934</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8374,36 +8374,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.003124085</v>
+        <v>0.003128365</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-6.6024e-05</v>
+        <v>-6.198999999999999e-05</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.000104602</v>
+        <v>0.000108302</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.000107236</v>
+        <v>0.000110997</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.010076417</v>
+        <v>0.010046329</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.009987769000000001</v>
+        <v>-0.009984653</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.000115493</v>
+        <v>0.000118553</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>1.7653e-05</v>
+        <v>2.0471e-05</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-8.0324e-05</v>
+        <v>-7.773799999999999e-05</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.000111085</v>
+        <v>-0.000108726</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8502,36 +8502,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.000524085</v>
+        <v>0.000528365</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-6.6024e-05</v>
+        <v>-6.198999999999999e-05</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.010104602</v>
+        <v>0.010108302</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.009892764</v>
+        <v>-0.009889003</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.010076417</v>
+        <v>0.010046329</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>1.2231e-05</v>
+        <v>1.5347e-05</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.009884507000000001</v>
+        <v>-0.009881447</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>1.7653e-05</v>
+        <v>2.0471e-05</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-8.0324e-05</v>
+        <v>-7.773799999999999e-05</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.009888915</v>
+        <v>0.009891274</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8896,10 +8896,10 @@
         <v>-0.038824832</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>-0.040460861</v>
+        <v>-0.040528634</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>-0.042237604</v>
+        <v>-0.042169951</v>
       </c>
       <c r="AI36" s="24" t="n">
         <v>-0.043731563</v>
@@ -9578,11 +9578,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>1890</v>
+        <v>1909</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,880원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,911원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1296720264082633</v>
+        <v>0.1296784476626306</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.01342097498616116</v>
+        <v>0.01342111303654409</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04177616281521523</v>
+        <v>0.04177617064608793</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19920,7 +19920,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34862,7 +34862,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42486,7 +42486,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="33">
@@ -42520,7 +42520,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>110.26</v>
+        <v>110.87</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/096350_model.xlsx
+++ b/argus/kship/models/096350_model.xlsx
@@ -4439,7 +4439,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19920,7 +19920,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/096350_model.xlsx
+++ b/argus/kship/models/096350_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 190576억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 190568억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 197880억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 197871억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 204706억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 204697억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 213745억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 213736억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 226612억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 226611억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 240663억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 240662억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 255328억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 255327억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 270076억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 270074억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 282250억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 282249억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 190576억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 190568억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 197880억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 197871억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 204706억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 204697억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 213745억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 213736억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 226612억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 226611억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 240663억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 240662억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 255328억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255327억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 270076억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 270074억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 282250억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 282249억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -5310,35 +5310,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5667,35 +5667,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5786,35 +5786,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5905,35 +5905,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6024,35 +6024,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6143,35 +6143,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6278,7 +6278,7 @@
         <v>1859</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1909</v>
+        <v>1877</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6551,7 +6551,7 @@
         <v>1800.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1894.5</v>
+        <v>1890.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6706,33 +6706,33 @@
         <v>0.195237238</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.363464245</v>
+        <v>0.36340798</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.029244203</v>
+        <v>0.029197139</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.182787785</v>
+        <v>0.182734835</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.180053645</v>
+        <v>0.179956108</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.189122271</v>
+        <v>0.189171344</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.216242169</v>
+        <v>0.216297787</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.247246844</v>
+        <v>0.247302682</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.26350374</v>
+        <v>0.263608184</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.24552332</v>
+        <v>0.245488617</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7017,20 +7017,20 @@
         <v>0.001219215</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.001237981</v>
+        <v>0.001238032</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.001234624</v>
+        <v>0.001234681</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.001208703</v>
+        <v>0.001208757</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.001239823</v>
+        <v>0.001239926</v>
       </c>
       <c r="AI23" s="24" t="n">
         <v>0.001214603</v>
@@ -7049,7 +7049,7 @@
         <v>0.001210218</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.001225934</v>
+        <v>0.001225968</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8377,17 +8377,17 @@
         <v>0.003128365</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-6.198999999999999e-05</v>
+        <v>-6.2012e-05</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.000108302</v>
+        <v>0.000108421</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.000110997</v>
+        <v>0.000110972</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.010046329</v>
+        <v>0.010046453</v>
       </c>
       <c r="AI32" s="30" t="n">
         <v>-0.009984653</v>
@@ -8397,13 +8397,13 @@
         <v>0.000118553</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>2.0471e-05</v>
+        <v>2.0472e-05</v>
       </c>
       <c r="AM32" s="30" t="n">
         <v>-7.773799999999999e-05</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.000108726</v>
+        <v>-0.000108783</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8505,17 +8505,17 @@
         <v>0.000528365</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-6.198999999999999e-05</v>
+        <v>-6.2012e-05</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.010108302</v>
+        <v>0.010108421</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.009889003</v>
+        <v>-0.009889027999999999</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.010046329</v>
+        <v>0.010046453</v>
       </c>
       <c r="AI33" s="30" t="n">
         <v>1.5347e-05</v>
@@ -8525,13 +8525,13 @@
         <v>-0.009881447</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>2.0471e-05</v>
+        <v>2.0472e-05</v>
       </c>
       <c r="AM33" s="30" t="n">
         <v>-7.773799999999999e-05</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.009891274</v>
+        <v>0.009891217000000001</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -9578,11 +9578,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>1909</v>
+        <v>1877</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,911원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,908원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1296784476626306</v>
+        <v>0.1296699952448883</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42486,7 +42486,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="33">
@@ -42520,7 +42520,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>110.87</v>
+        <v>109.85</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/096350_model.xlsx
+++ b/argus/kship/models/096350_model.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$107</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$106</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$93</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -657,61 +657,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 181135억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 181936억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 190568억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 192996억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 197871억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 201022억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 204697억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 207864억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 213736억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 215622억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 226611억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 226082억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 240662억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 238445억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 255327억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 252123억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 270074억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 266563억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 282249억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 279067억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1764,61 +1764,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 181135억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 181936억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 190568억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 192996억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 197871억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 201022억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 204697억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 207864억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 213736억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 215622억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 226611억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 226082억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 240662억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 238445억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 255327억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 252123억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 270074억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 266563억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 282249억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 279067억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -3439,82 +3439,82 @@
     </comment>
     <comment ref="E33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 159,155,279주 × 1/5(환산 — 2025Q4 1/5 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="G33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 159,155,279주 × 1/5(환산 — 2025Q4 1/5 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="H33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 159,155,279주 × 1/5(환산 — 2025Q4 1/5 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="I33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 159,155,279주 × 1/5(환산 — 2025Q4 1/5 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="J33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 159,155,279주 × 1/5(환산 — 2025Q4 1/5 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="L33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 159,155,279주 × 1/5(환산 — 2025Q4 1/5 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="M33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 159,155,279주 × 1/5(환산 — 2025Q4 1/5 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="N33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 159,155,279주 × 1/5(환산 — 2025Q4 1/5 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="O33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 159,155,279주 × 1/5(환산 — 2025Q4 1/5 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="Q33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 159,155,279주 × 1/5(환산 — 2025Q4 1/5 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="R33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 159,155,279주 × 1/5(환산 — 2025Q4 1/5 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="S33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 159,155,279주 × 1/5(환산 — 2025Q4 1/5 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="T33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 159,155,279주 × 1/5(환산 — 2025Q4 1/5 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="V33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 159,155,279주 × 1/5(환산 — 2025Q4 1/5 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="W33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 175,565,535주 × 1/5(환산 — 2025Q4 1/5 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="X33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 179,668,081주 × 1/5(환산 — 2025Q4 1/5 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="Y33" authorId="0" shapeId="0">
@@ -4439,7 +4439,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>· 밸류에이션 — PER 밴드 10.0/15.0/20.0배(sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 PER 중위 322.7배가 3~40 밖(턴어라운드 왜곡))) · COE 9.0% · 12M fwd EPS 가중 0.5(가정). 모델 산출값 구간이며 추천이 아니다</t>
+          <t>· 밸류에이션 — PER 밴드 10.0/15.0/20.0배(sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 PER 중위 105.0배가 3~40 밖(턴어라운드 왜곡))) · COE 9.0% · 12M fwd EPS 가중 0.5(가정). 모델 산출값 구간이며 추천이 아니다</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 지배주주순이익 face 누락 분기는 당기순이익 − 비지배 로 파생: 2024Q3, 2024Q4</t>
+          <t>한계: 모델 quality.warnings — 지배주주순이익 face 누락 분기는 당기순이익 − 비지배 로 파생: 2024Q3, 2024Q4 / 주식수 사건 환산: 2025Q4 1/5 병합(eps_reported 교차검증 confirmed) → 사건 전 실적 16분기의 주식수·EPS·BPS·DPS 를 비율 환산(IAS 33.64; 셀 kind estimate, basis 에 원주식수·비율)</t>
         </is>
       </c>
     </row>
@@ -6703,36 +6703,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.195237238</v>
+        <v>0.200541631</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.36340798</v>
+        <v>0.380793795</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.029197139</v>
+        <v>0.0456225</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.182734835</v>
+        <v>0.201002442</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.179956108</v>
+        <v>0.185133036</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.189171344</v>
+        <v>0.171427407</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.216297787</v>
+        <v>0.186163748</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.247302682</v>
+        <v>0.212944185</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.263608184</v>
+        <v>0.236265312</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245488617</v>
+        <v>0.234381522</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7014,42 +7014,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.001219215</v>
+        <v>0.001213828</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.001238032</v>
+        <v>0.001222444</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.001234681</v>
+        <v>0.001215286</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.001208757</v>
+        <v>0.001234459</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.001239926</v>
+        <v>0.001229055</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.001214603</v>
+        <v>0.001217476</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.001203098</v>
+        <v>0.001214283</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.001220344</v>
+        <v>0.001235824</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.001210218</v>
+        <v>0.00122614</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.001225968</v>
+        <v>0.001211745</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8374,36 +8374,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.003128365</v>
+        <v>0.003104454</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-6.2012e-05</v>
+        <v>-8.7233e-05</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.000108421</v>
+        <v>-0.009884656</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.000110972</v>
+        <v>0.010116382</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.010046453</v>
+        <v>8.4008e-05</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.009984653</v>
+        <v>5.1556e-05</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.000118553</v>
+        <v>0.000119802</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>2.0472e-05</v>
+        <v>2.0174e-05</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-7.773799999999999e-05</v>
+        <v>0.009920754</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.000108783</v>
+        <v>-0.000145395</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8502,36 +8502,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.000528365</v>
+        <v>0.000504454</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-6.2012e-05</v>
+        <v>-8.7233e-05</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.010108421</v>
+        <v>0.000115344</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.009889027999999999</v>
+        <v>0.000116382</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.010046453</v>
+        <v>8.4008e-05</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>1.5347e-05</v>
+        <v>5.1556e-05</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.009881447</v>
+        <v>0.000119802</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>2.0472e-05</v>
+        <v>0.010020174</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-7.773799999999999e-05</v>
+        <v>-7.924600000000001e-05</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.009891217000000001</v>
+        <v>-0.000145395</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8765,29 +8765,29 @@
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.010317309</v>
+        <v>0.010299998</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.010246218</v>
+        <v>0.010246393</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.010125337</v>
+        <v>0.010125509</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.009973470999999999</v>
+        <v>0.009956848000000001</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.009941482</v>
+        <v>0.009958437000000001</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.009860081999999999</v>
+        <v>0.009860245</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.009747509999999999</v>
+        <v>0.009747669</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.009572699</v>
+        <v>0.009588997</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8889,33 +8889,33 @@
         <v>-0.035924541</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>-0.037071886</v>
+        <v>-0.037009158</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>-0.038824832</v>
+        <v>-0.038822303</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>-0.040528634</v>
+        <v>-0.040458119</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>-0.042169951</v>
+        <v>-0.042163995</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>-0.043731563</v>
+        <v>-0.04379885</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>-0.046194185</v>
+        <v>-0.046190623</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>-0.048431436</v>
+        <v>-0.04842752</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>-0.050726485</v>
+        <v>-0.050807137</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>-0.053079126</v>
+        <v>-0.053168636</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 PER 중위 322.7배가 3~40 밖(턴어라운드 왜곡))</t>
+          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 PER 중위 105.0배가 3~40 밖(턴어라운드 왜곡))</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1296699952448883</v>
+        <v>0.129670371498173</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.01342111303654409</v>
+        <v>0.01342205540426584</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04177617064608793</v>
+        <v>0.04177651543000203</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO107"/>
+  <dimension ref="A1:AO106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15136,28 +15136,28 @@
         </is>
       </c>
       <c r="E52" s="18" t="n">
-        <v>61467.24</v>
+        <v>60711.81</v>
       </c>
       <c r="F52" s="37" t="n">
-        <v>61467.24</v>
+        <v>60711.81</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>61975.98</v>
+        <v>61150.24</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>61172.05</v>
+        <v>60322.05</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>61937.44</v>
+        <v>61087.44</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>59858.24</v>
+        <v>59008.24</v>
       </c>
       <c r="K52" s="37" t="n">
-        <v>59858.24</v>
+        <v>59008.24</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>59183.1</v>
+        <v>58333.1</v>
       </c>
       <c r="M52" s="18" t="n">
         <v>99422.78999999999</v>
@@ -15231,28 +15231,28 @@
         </is>
       </c>
       <c r="E53" s="18" t="n">
-        <v>54965.73</v>
+        <v>54210.3</v>
       </c>
       <c r="F53" s="37" t="n">
-        <v>54965.73</v>
+        <v>54210.3</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>60128.62</v>
+        <v>59302.88</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>59635.21</v>
+        <v>58785.21</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>59340.59</v>
+        <v>58490.59</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>56852.86</v>
+        <v>56002.86</v>
       </c>
       <c r="K53" s="37" t="n">
-        <v>56852.86</v>
+        <v>56002.86</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>54731.72</v>
+        <v>53881.72</v>
       </c>
       <c r="M53" s="18" t="n">
         <v>93816.24000000001</v>
@@ -15417,69 +15417,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>사채</t>
-        </is>
-      </c>
-      <c r="E55" s="18" t="n">
-        <v>755.4299999999999</v>
-      </c>
-      <c r="F55" s="37" t="n">
-        <v>755.4299999999999</v>
-      </c>
+          <t>단기투자자산(공정가치)</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="n"/>
       <c r="G55" s="18" t="n">
-        <v>825.74</v>
+        <v>0</v>
       </c>
       <c r="H55" s="18" t="n">
-        <v>850</v>
-      </c>
-      <c r="I55" s="18" t="n">
-        <v>850</v>
-      </c>
-      <c r="J55" s="18" t="n">
-        <v>850</v>
-      </c>
-      <c r="K55" s="37" t="n">
-        <v>850</v>
-      </c>
-      <c r="L55" s="18" t="n">
-        <v>850</v>
-      </c>
-      <c r="O55" s="18" t="n">
-        <v>3432.63</v>
-      </c>
-      <c r="P55" s="37" t="n">
-        <v>3432.63</v>
-      </c>
-      <c r="Q55" s="18" t="n">
-        <v>7864.33</v>
-      </c>
-      <c r="R55" s="18" t="n">
-        <v>8513.1</v>
-      </c>
-      <c r="S55" s="18" t="n">
-        <v>8838.370000000001</v>
-      </c>
-      <c r="T55" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="U55" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="K55" s="9" t="n"/>
+      <c r="P55" s="9" t="n"/>
+      <c r="U55" s="9" t="n"/>
+      <c r="Z55" s="9" t="n"/>
+      <c r="AB55" s="5" t="n"/>
       <c r="AC55" s="10" t="n"/>
       <c r="AD55" s="10" t="n"/>
       <c r="AE55" s="11" t="n"/>
@@ -15500,7 +15452,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>단기투자자산(공정가치)</t>
+          <t>종속기업및관계기업투자</t>
         </is>
       </c>
       <c r="F56" s="9" t="n"/>
@@ -15535,21 +15487,47 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>종속기업및관계기업투자</t>
+          <t>유동성장기부채</t>
         </is>
       </c>
       <c r="F57" s="9" t="n"/>
-      <c r="G57" s="18" t="n">
+      <c r="K57" s="9" t="n"/>
+      <c r="M57" s="18" t="n">
+        <v>50362.44</v>
+      </c>
+      <c r="O57" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="18" t="n">
+      <c r="P57" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="K57" s="9" t="n"/>
-      <c r="P57" s="9" t="n"/>
-      <c r="U57" s="9" t="n"/>
-      <c r="Z57" s="9" t="n"/>
-      <c r="AB57" s="5" t="n"/>
+      <c r="T57" s="18" t="n">
+        <v>13294.17</v>
+      </c>
+      <c r="U57" s="37" t="n">
+        <v>13294.17</v>
+      </c>
+      <c r="V57" s="18" t="n">
+        <v>13576.36</v>
+      </c>
+      <c r="W57" s="18" t="n">
+        <v>10663.32</v>
+      </c>
+      <c r="X57" s="18" t="n">
+        <v>10072.26</v>
+      </c>
+      <c r="Y57" s="18" t="n">
+        <v>10213.15</v>
+      </c>
+      <c r="Z57" s="37" t="n">
+        <v>10213.15</v>
+      </c>
+      <c r="AA57" s="18" t="n">
+        <v>7955.36</v>
+      </c>
+      <c r="AB57" s="19" t="n">
+        <v>8398.42</v>
+      </c>
       <c r="AC57" s="10" t="n"/>
       <c r="AD57" s="10" t="n"/>
       <c r="AE57" s="11" t="n"/>
@@ -15570,46 +15548,52 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>유동성장기부채</t>
+          <t>유동파생상품자산</t>
         </is>
       </c>
       <c r="F58" s="9" t="n"/>
       <c r="K58" s="9" t="n"/>
-      <c r="M58" s="18" t="n">
-        <v>50362.44</v>
-      </c>
       <c r="O58" s="18" t="n">
+        <v>247.04</v>
+      </c>
+      <c r="P58" s="37" t="n">
+        <v>247.04</v>
+      </c>
+      <c r="Q58" s="18" t="n">
+        <v>913.29</v>
+      </c>
+      <c r="R58" s="18" t="n">
+        <v>1199.48</v>
+      </c>
+      <c r="S58" s="18" t="n">
+        <v>1199.48</v>
+      </c>
+      <c r="T58" s="18" t="n">
+        <v>60.73</v>
+      </c>
+      <c r="U58" s="37" t="n">
+        <v>60.73</v>
+      </c>
+      <c r="V58" s="18" t="n">
+        <v>60.73</v>
+      </c>
+      <c r="W58" s="18" t="n">
+        <v>728.72</v>
+      </c>
+      <c r="X58" s="18" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Y58" s="18" t="n">
+        <v>156.48</v>
+      </c>
+      <c r="Z58" s="37" t="n">
+        <v>156.48</v>
+      </c>
+      <c r="AA58" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="P58" s="37" t="n">
+      <c r="AB58" s="19" t="n">
         <v>0</v>
-      </c>
-      <c r="T58" s="18" t="n">
-        <v>13294.17</v>
-      </c>
-      <c r="U58" s="37" t="n">
-        <v>13294.17</v>
-      </c>
-      <c r="V58" s="18" t="n">
-        <v>13576.36</v>
-      </c>
-      <c r="W58" s="18" t="n">
-        <v>10663.32</v>
-      </c>
-      <c r="X58" s="18" t="n">
-        <v>10072.26</v>
-      </c>
-      <c r="Y58" s="18" t="n">
-        <v>10213.15</v>
-      </c>
-      <c r="Z58" s="37" t="n">
-        <v>10213.15</v>
-      </c>
-      <c r="AA58" s="18" t="n">
-        <v>7955.36</v>
-      </c>
-      <c r="AB58" s="19" t="n">
-        <v>8398.42</v>
       </c>
       <c r="AC58" s="10" t="n"/>
       <c r="AD58" s="10" t="n"/>
@@ -15631,52 +15615,52 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>유동파생상품자산</t>
+          <t>단기파생상품부채</t>
         </is>
       </c>
       <c r="F59" s="9" t="n"/>
       <c r="K59" s="9" t="n"/>
       <c r="O59" s="18" t="n">
-        <v>247.04</v>
+        <v>4025.56</v>
       </c>
       <c r="P59" s="37" t="n">
-        <v>247.04</v>
+        <v>4025.56</v>
       </c>
       <c r="Q59" s="18" t="n">
-        <v>913.29</v>
+        <v>11287.16</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>1199.48</v>
+        <v>8734.860000000001</v>
       </c>
       <c r="S59" s="18" t="n">
-        <v>1199.48</v>
+        <v>8734.860000000001</v>
       </c>
       <c r="T59" s="18" t="n">
-        <v>60.73</v>
+        <v>4891.67</v>
       </c>
       <c r="U59" s="37" t="n">
-        <v>60.73</v>
+        <v>4891.67</v>
       </c>
       <c r="V59" s="18" t="n">
-        <v>60.73</v>
+        <v>4891.67</v>
       </c>
       <c r="W59" s="18" t="n">
-        <v>728.72</v>
+        <v>3532.55</v>
       </c>
       <c r="X59" s="18" t="n">
-        <v>2.57</v>
+        <v>2083.94</v>
       </c>
       <c r="Y59" s="18" t="n">
-        <v>156.48</v>
+        <v>2738.27</v>
       </c>
       <c r="Z59" s="37" t="n">
-        <v>156.48</v>
+        <v>2738.27</v>
       </c>
       <c r="AA59" s="18" t="n">
-        <v>0</v>
+        <v>2132.93</v>
       </c>
       <c r="AB59" s="19" t="n">
-        <v>0</v>
+        <v>2343.96</v>
       </c>
       <c r="AC59" s="10" t="n"/>
       <c r="AD59" s="10" t="n"/>
@@ -15698,52 +15682,46 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>단기파생상품부채</t>
+          <t>사채</t>
         </is>
       </c>
       <c r="F60" s="9" t="n"/>
       <c r="K60" s="9" t="n"/>
       <c r="O60" s="18" t="n">
-        <v>4025.56</v>
+        <v>3432.63</v>
       </c>
       <c r="P60" s="37" t="n">
-        <v>4025.56</v>
+        <v>3432.63</v>
       </c>
       <c r="Q60" s="18" t="n">
-        <v>11287.16</v>
+        <v>7864.33</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>8734.860000000001</v>
+        <v>8513.1</v>
       </c>
       <c r="S60" s="18" t="n">
-        <v>8734.860000000001</v>
+        <v>8838.370000000001</v>
       </c>
       <c r="T60" s="18" t="n">
-        <v>4891.67</v>
+        <v>0</v>
       </c>
       <c r="U60" s="37" t="n">
-        <v>4891.67</v>
+        <v>0</v>
       </c>
       <c r="V60" s="18" t="n">
-        <v>4891.67</v>
-      </c>
-      <c r="W60" s="18" t="n">
-        <v>3532.55</v>
-      </c>
-      <c r="X60" s="18" t="n">
-        <v>2083.94</v>
+        <v>0</v>
       </c>
       <c r="Y60" s="18" t="n">
-        <v>2738.27</v>
+        <v>0</v>
       </c>
       <c r="Z60" s="37" t="n">
-        <v>2738.27</v>
+        <v>0</v>
       </c>
       <c r="AA60" s="18" t="n">
-        <v>2132.93</v>
+        <v>0</v>
       </c>
       <c r="AB60" s="19" t="n">
-        <v>2343.96</v>
+        <v>0</v>
       </c>
       <c r="AC60" s="10" t="n"/>
       <c r="AD60" s="10" t="n"/>
@@ -15765,28 +15743,78 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>장기금융부채(face)</t>
-        </is>
+          <t>매출액(수익)</t>
+        </is>
+      </c>
+      <c r="E61" s="18" t="n">
+        <v>14534.94</v>
       </c>
       <c r="F61" s="9" t="n"/>
-      <c r="K61" s="9" t="n"/>
-      <c r="P61" s="9" t="n"/>
-      <c r="U61" s="9" t="n"/>
+      <c r="G61" s="18" t="n">
+        <v>12500.03</v>
+      </c>
+      <c r="H61" s="18" t="n">
+        <v>11730.6</v>
+      </c>
+      <c r="I61" s="18" t="n">
+        <v>12798.42</v>
+      </c>
+      <c r="J61" s="18" t="n">
+        <v>15727.04</v>
+      </c>
+      <c r="K61" s="37" t="n">
+        <v>52756.09</v>
+      </c>
+      <c r="L61" s="18" t="n">
+        <v>19766.41</v>
+      </c>
+      <c r="M61" s="18" t="n">
+        <v>17099.02</v>
+      </c>
+      <c r="N61" s="18" t="n">
+        <v>17302.73</v>
+      </c>
+      <c r="O61" s="18" t="n">
+        <v>17546.94</v>
+      </c>
+      <c r="P61" s="37" t="n">
+        <v>71715.10000000001</v>
+      </c>
+      <c r="Q61" s="18" t="n">
+        <v>16739.95</v>
+      </c>
+      <c r="R61" s="18" t="n">
+        <v>14064.24</v>
+      </c>
+      <c r="S61" s="18" t="n">
+        <v>12924.18</v>
+      </c>
+      <c r="T61" s="18" t="n">
+        <v>17670.18</v>
+      </c>
+      <c r="U61" s="37" t="n">
+        <v>61398.55</v>
+      </c>
       <c r="V61" s="18" t="n">
-        <v>20251.36</v>
+        <v>10329.01</v>
       </c>
       <c r="W61" s="18" t="n">
-        <v>17157.01</v>
+        <v>14619.54</v>
       </c>
       <c r="X61" s="18" t="n">
-        <v>16932.57</v>
-      </c>
-      <c r="Z61" s="9" t="n"/>
+        <v>17155.59</v>
+      </c>
+      <c r="Y61" s="18" t="n">
+        <v>17773.11</v>
+      </c>
+      <c r="Z61" s="37" t="n">
+        <v>59877.25</v>
+      </c>
       <c r="AA61" s="18" t="n">
-        <v>38870</v>
+        <v>21247.63</v>
       </c>
       <c r="AB61" s="19" t="n">
-        <v>41720</v>
+        <v>18885.89</v>
       </c>
       <c r="AC61" s="10" t="n"/>
       <c r="AD61" s="10" t="n"/>
@@ -15808,78 +15836,78 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>매출액(수익)</t>
+          <t>매출원가</t>
         </is>
       </c>
       <c r="E62" s="18" t="n">
-        <v>14534.94</v>
+        <v>17624.61</v>
       </c>
       <c r="F62" s="9" t="n"/>
       <c r="G62" s="18" t="n">
-        <v>12500.03</v>
+        <v>12307.05</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>11730.6</v>
+        <v>11747.91</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>12798.42</v>
+        <v>12346.46</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>15727.04</v>
+        <v>14109.24</v>
       </c>
       <c r="K62" s="37" t="n">
-        <v>52756.09</v>
+        <v>50510.66</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>19766.41</v>
+        <v>15726.9</v>
       </c>
       <c r="M62" s="18" t="n">
-        <v>17099.02</v>
+        <v>12811.42</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>17302.73</v>
+        <v>14536.99</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>17546.94</v>
+        <v>14740</v>
       </c>
       <c r="P62" s="37" t="n">
-        <v>71715.10000000001</v>
+        <v>57815.31</v>
       </c>
       <c r="Q62" s="18" t="n">
-        <v>16739.95</v>
+        <v>13914.53</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>14064.24</v>
+        <v>11754.49</v>
       </c>
       <c r="S62" s="18" t="n">
-        <v>12924.18</v>
+        <v>11711.29</v>
       </c>
       <c r="T62" s="18" t="n">
-        <v>17670.18</v>
+        <v>14912.22</v>
       </c>
       <c r="U62" s="37" t="n">
-        <v>61398.55</v>
+        <v>52292.53</v>
       </c>
       <c r="V62" s="18" t="n">
-        <v>10329.01</v>
+        <v>9301.85</v>
       </c>
       <c r="W62" s="18" t="n">
-        <v>14619.54</v>
+        <v>12404.24</v>
       </c>
       <c r="X62" s="18" t="n">
-        <v>17155.59</v>
+        <v>13302.11</v>
       </c>
       <c r="Y62" s="18" t="n">
-        <v>17773.11</v>
+        <v>15165.92</v>
       </c>
       <c r="Z62" s="37" t="n">
-        <v>59877.25</v>
+        <v>50174.12</v>
       </c>
       <c r="AA62" s="18" t="n">
-        <v>21247.63</v>
+        <v>17167.26</v>
       </c>
       <c r="AB62" s="19" t="n">
-        <v>18885.89</v>
+        <v>17669.18</v>
       </c>
       <c r="AC62" s="10" t="n"/>
       <c r="AD62" s="10" t="n"/>
@@ -15901,78 +15929,78 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>매출원가</t>
+          <t>매출총이익</t>
         </is>
       </c>
       <c r="E63" s="18" t="n">
-        <v>17624.61</v>
+        <v>-3089.67</v>
       </c>
       <c r="F63" s="9" t="n"/>
       <c r="G63" s="18" t="n">
-        <v>12307.05</v>
+        <v>192.98</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>11747.91</v>
+        <v>-17.31</v>
       </c>
       <c r="I63" s="18" t="n">
-        <v>12346.46</v>
+        <v>451.97</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>14109.24</v>
+        <v>1617.8</v>
       </c>
       <c r="K63" s="37" t="n">
-        <v>50510.66</v>
+        <v>2245.44</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>15726.9</v>
+        <v>4039.51</v>
       </c>
       <c r="M63" s="18" t="n">
-        <v>12811.42</v>
+        <v>4287.6</v>
       </c>
       <c r="N63" s="18" t="n">
-        <v>14536.99</v>
+        <v>2765.74</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>14740</v>
+        <v>2806.94</v>
       </c>
       <c r="P63" s="37" t="n">
-        <v>57815.31</v>
+        <v>13899.79</v>
       </c>
       <c r="Q63" s="18" t="n">
-        <v>13914.53</v>
+        <v>2825.42</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>11754.49</v>
+        <v>2309.75</v>
       </c>
       <c r="S63" s="18" t="n">
-        <v>11711.29</v>
+        <v>1212.89</v>
       </c>
       <c r="T63" s="18" t="n">
-        <v>14912.22</v>
+        <v>2757.96</v>
       </c>
       <c r="U63" s="37" t="n">
-        <v>52292.53</v>
+        <v>9106.02</v>
       </c>
       <c r="V63" s="18" t="n">
-        <v>9301.85</v>
+        <v>1027.16</v>
       </c>
       <c r="W63" s="18" t="n">
-        <v>12404.24</v>
+        <v>2215.3</v>
       </c>
       <c r="X63" s="18" t="n">
-        <v>13302.11</v>
+        <v>3853.48</v>
       </c>
       <c r="Y63" s="18" t="n">
-        <v>15165.92</v>
+        <v>2607.19</v>
       </c>
       <c r="Z63" s="37" t="n">
-        <v>50174.12</v>
+        <v>9703.129999999999</v>
       </c>
       <c r="AA63" s="18" t="n">
-        <v>17167.26</v>
+        <v>4080.37</v>
       </c>
       <c r="AB63" s="19" t="n">
-        <v>17669.18</v>
+        <v>1216.71</v>
       </c>
       <c r="AC63" s="10" t="n"/>
       <c r="AD63" s="10" t="n"/>
@@ -15994,78 +16022,78 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>매출총이익</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="E64" s="18" t="n">
-        <v>-3089.67</v>
+        <v>2297.32</v>
       </c>
       <c r="F64" s="9" t="n"/>
       <c r="G64" s="18" t="n">
-        <v>192.98</v>
+        <v>1826.59</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>-17.31</v>
+        <v>1586.19</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>451.97</v>
+        <v>1755.76</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>1617.8</v>
+        <v>1818.32</v>
       </c>
       <c r="K64" s="37" t="n">
-        <v>2245.44</v>
+        <v>6986.86</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>4039.51</v>
+        <v>1855.03</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>4287.6</v>
+        <v>2020.1</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>2765.74</v>
+        <v>2024.52</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>2806.94</v>
+        <v>2403.65</v>
       </c>
       <c r="P64" s="37" t="n">
-        <v>13899.79</v>
+        <v>8303.299999999999</v>
       </c>
       <c r="Q64" s="18" t="n">
-        <v>2825.42</v>
+        <v>1867.24</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>2309.75</v>
+        <v>2463.15</v>
       </c>
       <c r="S64" s="18" t="n">
-        <v>1212.89</v>
+        <v>1795.51</v>
       </c>
       <c r="T64" s="18" t="n">
-        <v>2757.96</v>
+        <v>2543.36</v>
       </c>
       <c r="U64" s="37" t="n">
-        <v>9106.02</v>
+        <v>8669.26</v>
       </c>
       <c r="V64" s="18" t="n">
-        <v>1027.16</v>
+        <v>2194.59</v>
       </c>
       <c r="W64" s="18" t="n">
-        <v>2215.3</v>
+        <v>2535.3</v>
       </c>
       <c r="X64" s="18" t="n">
-        <v>3853.48</v>
+        <v>2681.08</v>
       </c>
       <c r="Y64" s="18" t="n">
-        <v>2607.19</v>
+        <v>2435.91</v>
       </c>
       <c r="Z64" s="37" t="n">
-        <v>9703.129999999999</v>
+        <v>9846.879999999999</v>
       </c>
       <c r="AA64" s="18" t="n">
-        <v>4080.37</v>
+        <v>2598.33</v>
       </c>
       <c r="AB64" s="19" t="n">
-        <v>1216.71</v>
+        <v>1352.6</v>
       </c>
       <c r="AC64" s="10" t="n"/>
       <c r="AD64" s="10" t="n"/>
@@ -16087,78 +16115,78 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>영업이익</t>
         </is>
       </c>
       <c r="E65" s="18" t="n">
-        <v>2297.32</v>
+        <v>-5386.99</v>
       </c>
       <c r="F65" s="9" t="n"/>
       <c r="G65" s="18" t="n">
-        <v>1826.59</v>
+        <v>-1633.61</v>
       </c>
       <c r="H65" s="18" t="n">
-        <v>1586.19</v>
+        <v>-1603.5</v>
       </c>
       <c r="I65" s="18" t="n">
-        <v>1755.76</v>
+        <v>-1303.79</v>
       </c>
       <c r="J65" s="18" t="n">
-        <v>1818.32</v>
+        <v>-200.52</v>
       </c>
       <c r="K65" s="37" t="n">
-        <v>6986.86</v>
+        <v>-4741.42</v>
       </c>
       <c r="L65" s="18" t="n">
-        <v>1855.03</v>
+        <v>2184.48</v>
       </c>
       <c r="M65" s="18" t="n">
-        <v>2020.1</v>
+        <v>2267.5</v>
       </c>
       <c r="N65" s="18" t="n">
-        <v>2024.52</v>
+        <v>741.22</v>
       </c>
       <c r="O65" s="18" t="n">
-        <v>2403.65</v>
+        <v>403.29</v>
       </c>
       <c r="P65" s="37" t="n">
-        <v>8303.299999999999</v>
+        <v>5596.49</v>
       </c>
       <c r="Q65" s="18" t="n">
-        <v>1867.24</v>
+        <v>958.1799999999999</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>2463.15</v>
+        <v>-153.39</v>
       </c>
       <c r="S65" s="18" t="n">
-        <v>1795.51</v>
+        <v>-582.62</v>
       </c>
       <c r="T65" s="18" t="n">
-        <v>2543.36</v>
+        <v>214.6</v>
       </c>
       <c r="U65" s="37" t="n">
-        <v>8669.26</v>
+        <v>436.77</v>
       </c>
       <c r="V65" s="18" t="n">
-        <v>2194.59</v>
+        <v>-1167.43</v>
       </c>
       <c r="W65" s="18" t="n">
-        <v>2535.3</v>
+        <v>-320</v>
       </c>
       <c r="X65" s="18" t="n">
-        <v>2681.08</v>
+        <v>1172.4</v>
       </c>
       <c r="Y65" s="18" t="n">
-        <v>2435.91</v>
+        <v>171.28</v>
       </c>
       <c r="Z65" s="37" t="n">
-        <v>9846.879999999999</v>
+        <v>-143.75</v>
       </c>
       <c r="AA65" s="18" t="n">
-        <v>2598.33</v>
+        <v>1482.04</v>
       </c>
       <c r="AB65" s="19" t="n">
-        <v>1352.6</v>
+        <v>-135.88</v>
       </c>
       <c r="AC65" s="10" t="n"/>
       <c r="AD65" s="10" t="n"/>
@@ -16180,78 +16208,78 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>영업이익</t>
+          <t>기타영업외수익</t>
         </is>
       </c>
       <c r="E66" s="18" t="n">
-        <v>-5386.99</v>
+        <v>257.34</v>
       </c>
       <c r="F66" s="9" t="n"/>
       <c r="G66" s="18" t="n">
-        <v>-1633.61</v>
+        <v>60.59</v>
       </c>
       <c r="H66" s="18" t="n">
-        <v>-1603.5</v>
+        <v>422.84</v>
       </c>
       <c r="I66" s="18" t="n">
-        <v>-1303.79</v>
+        <v>235.49</v>
       </c>
       <c r="J66" s="18" t="n">
-        <v>-200.52</v>
+        <v>-22.82</v>
       </c>
       <c r="K66" s="37" t="n">
-        <v>-4741.42</v>
+        <v>696.1</v>
       </c>
       <c r="L66" s="18" t="n">
-        <v>2184.48</v>
+        <v>294.87</v>
       </c>
       <c r="M66" s="18" t="n">
-        <v>2267.5</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="N66" s="18" t="n">
-        <v>741.22</v>
+        <v>62.94</v>
       </c>
       <c r="O66" s="18" t="n">
-        <v>403.29</v>
+        <v>367.07</v>
       </c>
       <c r="P66" s="37" t="n">
-        <v>5596.49</v>
+        <v>794.2</v>
       </c>
       <c r="Q66" s="18" t="n">
-        <v>958.1799999999999</v>
+        <v>579.73</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>-153.39</v>
+        <v>101.24</v>
       </c>
       <c r="S66" s="18" t="n">
-        <v>-582.62</v>
+        <v>53.61</v>
       </c>
       <c r="T66" s="18" t="n">
-        <v>214.6</v>
+        <v>-96.48</v>
       </c>
       <c r="U66" s="37" t="n">
-        <v>436.77</v>
+        <v>638.1</v>
       </c>
       <c r="V66" s="18" t="n">
-        <v>-1167.43</v>
+        <v>93.08</v>
       </c>
       <c r="W66" s="18" t="n">
-        <v>-320</v>
+        <v>65.78</v>
       </c>
       <c r="X66" s="18" t="n">
-        <v>1172.4</v>
+        <v>319.32</v>
       </c>
       <c r="Y66" s="18" t="n">
-        <v>171.28</v>
+        <v>301.15</v>
       </c>
       <c r="Z66" s="37" t="n">
-        <v>-143.75</v>
+        <v>779.33</v>
       </c>
       <c r="AA66" s="18" t="n">
-        <v>1482.04</v>
+        <v>242.22</v>
       </c>
       <c r="AB66" s="19" t="n">
-        <v>-135.88</v>
+        <v>146</v>
       </c>
       <c r="AC66" s="10" t="n"/>
       <c r="AD66" s="10" t="n"/>
@@ -16273,78 +16301,78 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>기타영업외수익</t>
+          <t>기타영업외비용</t>
         </is>
       </c>
       <c r="E67" s="18" t="n">
-        <v>257.34</v>
+        <v>4487.68</v>
       </c>
       <c r="F67" s="9" t="n"/>
       <c r="G67" s="18" t="n">
-        <v>60.59</v>
+        <v>52.76</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>422.84</v>
+        <v>93.41</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>235.49</v>
+        <v>67.66</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-22.82</v>
+        <v>438.95</v>
       </c>
       <c r="K67" s="37" t="n">
-        <v>696.1</v>
+        <v>652.78</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>294.87</v>
+        <v>164.36</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>69.31999999999999</v>
+        <v>155.99</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>62.94</v>
+        <v>49.41</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>367.07</v>
+        <v>752.87</v>
       </c>
       <c r="P67" s="37" t="n">
-        <v>794.2</v>
+        <v>1122.63</v>
       </c>
       <c r="Q67" s="18" t="n">
-        <v>579.73</v>
+        <v>223.52</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>101.24</v>
+        <v>51.34</v>
       </c>
       <c r="S67" s="18" t="n">
-        <v>53.61</v>
+        <v>-41.68</v>
       </c>
       <c r="T67" s="18" t="n">
-        <v>-96.48</v>
+        <v>655.47</v>
       </c>
       <c r="U67" s="37" t="n">
-        <v>638.1</v>
+        <v>888.65</v>
       </c>
       <c r="V67" s="18" t="n">
-        <v>93.08</v>
+        <v>53.44</v>
       </c>
       <c r="W67" s="18" t="n">
-        <v>65.78</v>
+        <v>232.25</v>
       </c>
       <c r="X67" s="18" t="n">
-        <v>319.32</v>
+        <v>59.04</v>
       </c>
       <c r="Y67" s="18" t="n">
-        <v>301.15</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="Z67" s="37" t="n">
-        <v>779.33</v>
+        <v>414.83</v>
       </c>
       <c r="AA67" s="18" t="n">
-        <v>242.22</v>
+        <v>104.75</v>
       </c>
       <c r="AB67" s="19" t="n">
-        <v>146</v>
+        <v>103.96</v>
       </c>
       <c r="AC67" s="10" t="n"/>
       <c r="AD67" s="10" t="n"/>
@@ -16366,78 +16394,78 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>기타영업외비용</t>
+          <t>금융수익</t>
         </is>
       </c>
       <c r="E68" s="18" t="n">
-        <v>4487.68</v>
+        <v>28.13</v>
       </c>
       <c r="F68" s="9" t="n"/>
       <c r="G68" s="18" t="n">
-        <v>52.76</v>
+        <v>45.74</v>
       </c>
       <c r="H68" s="18" t="n">
-        <v>93.41</v>
+        <v>35.16</v>
       </c>
       <c r="I68" s="18" t="n">
-        <v>67.66</v>
+        <v>46.22</v>
       </c>
       <c r="J68" s="18" t="n">
-        <v>438.95</v>
+        <v>296.48</v>
       </c>
       <c r="K68" s="37" t="n">
-        <v>652.78</v>
+        <v>423.6</v>
       </c>
       <c r="L68" s="18" t="n">
-        <v>164.36</v>
+        <v>24.42</v>
       </c>
       <c r="M68" s="18" t="n">
-        <v>155.99</v>
+        <v>37.73</v>
       </c>
       <c r="N68" s="18" t="n">
-        <v>49.41</v>
+        <v>76.97</v>
       </c>
       <c r="O68" s="18" t="n">
-        <v>752.87</v>
+        <v>1179</v>
       </c>
       <c r="P68" s="37" t="n">
-        <v>1122.63</v>
+        <v>1318.12</v>
       </c>
       <c r="Q68" s="18" t="n">
-        <v>223.52</v>
+        <v>15.33</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>51.34</v>
+        <v>3026.96</v>
       </c>
       <c r="S68" s="18" t="n">
-        <v>-41.68</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="T68" s="18" t="n">
-        <v>655.47</v>
+        <v>-817.8200000000001</v>
       </c>
       <c r="U68" s="37" t="n">
-        <v>888.65</v>
+        <v>2324.4</v>
       </c>
       <c r="V68" s="18" t="n">
-        <v>53.44</v>
+        <v>171.8</v>
       </c>
       <c r="W68" s="18" t="n">
-        <v>232.25</v>
+        <v>1716.55</v>
       </c>
       <c r="X68" s="18" t="n">
-        <v>59.04</v>
+        <v>516.65</v>
       </c>
       <c r="Y68" s="18" t="n">
-        <v>70.09999999999999</v>
+        <v>-476.91</v>
       </c>
       <c r="Z68" s="37" t="n">
-        <v>414.83</v>
+        <v>1928.09</v>
       </c>
       <c r="AA68" s="18" t="n">
-        <v>104.75</v>
+        <v>70.25</v>
       </c>
       <c r="AB68" s="19" t="n">
-        <v>103.96</v>
+        <v>388.24</v>
       </c>
       <c r="AC68" s="10" t="n"/>
       <c r="AD68" s="10" t="n"/>
@@ -16459,78 +16487,78 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>금융수익</t>
+          <t>금융비용</t>
         </is>
       </c>
       <c r="E69" s="18" t="n">
-        <v>28.13</v>
+        <v>745.47</v>
       </c>
       <c r="F69" s="9" t="n"/>
       <c r="G69" s="18" t="n">
-        <v>45.74</v>
+        <v>679.83</v>
       </c>
       <c r="H69" s="18" t="n">
-        <v>35.16</v>
+        <v>717.98</v>
       </c>
       <c r="I69" s="18" t="n">
-        <v>46.22</v>
+        <v>744.96</v>
       </c>
       <c r="J69" s="18" t="n">
-        <v>296.48</v>
+        <v>892.75</v>
       </c>
       <c r="K69" s="37" t="n">
-        <v>423.6</v>
+        <v>3035.52</v>
       </c>
       <c r="L69" s="18" t="n">
-        <v>24.42</v>
+        <v>876.98</v>
       </c>
       <c r="M69" s="18" t="n">
-        <v>37.73</v>
+        <v>866.79</v>
       </c>
       <c r="N69" s="18" t="n">
-        <v>76.97</v>
+        <v>880.53</v>
       </c>
       <c r="O69" s="18" t="n">
-        <v>1179</v>
+        <v>1160.98</v>
       </c>
       <c r="P69" s="37" t="n">
-        <v>1318.12</v>
+        <v>3785.28</v>
       </c>
       <c r="Q69" s="18" t="n">
-        <v>15.33</v>
+        <v>875.22</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>3026.96</v>
+        <v>1536.06</v>
       </c>
       <c r="S69" s="18" t="n">
-        <v>99.93000000000001</v>
+        <v>1100.78</v>
       </c>
       <c r="T69" s="18" t="n">
-        <v>-817.8200000000001</v>
+        <v>1709.02</v>
       </c>
       <c r="U69" s="37" t="n">
-        <v>2324.4</v>
+        <v>5221.08</v>
       </c>
       <c r="V69" s="18" t="n">
-        <v>171.8</v>
+        <v>830.12</v>
       </c>
       <c r="W69" s="18" t="n">
-        <v>1716.55</v>
+        <v>7104</v>
       </c>
       <c r="X69" s="18" t="n">
-        <v>516.65</v>
+        <v>1308.44</v>
       </c>
       <c r="Y69" s="18" t="n">
-        <v>-476.91</v>
+        <v>682.37</v>
       </c>
       <c r="Z69" s="37" t="n">
-        <v>1928.09</v>
+        <v>9924.93</v>
       </c>
       <c r="AA69" s="18" t="n">
-        <v>70.25</v>
+        <v>649.42</v>
       </c>
       <c r="AB69" s="19" t="n">
-        <v>388.24</v>
+        <v>1437.12</v>
       </c>
       <c r="AC69" s="10" t="n"/>
       <c r="AD69" s="10" t="n"/>
@@ -16552,78 +16580,78 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>금융비용</t>
+          <t>법인세비용차감전계속사업이익</t>
         </is>
       </c>
       <c r="E70" s="18" t="n">
-        <v>745.47</v>
+        <v>-10634.67</v>
       </c>
       <c r="F70" s="9" t="n"/>
       <c r="G70" s="18" t="n">
-        <v>679.83</v>
+        <v>-2259.86</v>
       </c>
       <c r="H70" s="18" t="n">
-        <v>717.98</v>
+        <v>-1956.9</v>
       </c>
       <c r="I70" s="18" t="n">
-        <v>744.96</v>
+        <v>-1834.71</v>
       </c>
       <c r="J70" s="18" t="n">
-        <v>892.75</v>
+        <v>-1775.63</v>
       </c>
       <c r="K70" s="37" t="n">
-        <v>3035.52</v>
+        <v>-7827.1</v>
       </c>
       <c r="L70" s="18" t="n">
-        <v>876.98</v>
+        <v>1462.43</v>
       </c>
       <c r="M70" s="18" t="n">
-        <v>866.79</v>
+        <v>1351.76</v>
       </c>
       <c r="N70" s="18" t="n">
-        <v>880.53</v>
+        <v>-48.81</v>
       </c>
       <c r="O70" s="18" t="n">
-        <v>1160.98</v>
+        <v>35.51</v>
       </c>
       <c r="P70" s="37" t="n">
-        <v>3785.28</v>
+        <v>2800.89</v>
       </c>
       <c r="Q70" s="18" t="n">
-        <v>875.22</v>
+        <v>454.5</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>1536.06</v>
+        <v>1387.4</v>
       </c>
       <c r="S70" s="18" t="n">
-        <v>1100.78</v>
+        <v>-1488.18</v>
       </c>
       <c r="T70" s="18" t="n">
-        <v>1709.02</v>
+        <v>-3064.22</v>
       </c>
       <c r="U70" s="37" t="n">
-        <v>5221.08</v>
+        <v>-2710.5</v>
       </c>
       <c r="V70" s="18" t="n">
-        <v>830.12</v>
+        <v>-1786.1</v>
       </c>
       <c r="W70" s="18" t="n">
-        <v>7104</v>
+        <v>-5873.93</v>
       </c>
       <c r="X70" s="18" t="n">
-        <v>1308.44</v>
+        <v>640.89</v>
       </c>
       <c r="Y70" s="18" t="n">
-        <v>682.37</v>
+        <v>-756.9299999999999</v>
       </c>
       <c r="Z70" s="37" t="n">
-        <v>9924.93</v>
+        <v>-7776.07</v>
       </c>
       <c r="AA70" s="18" t="n">
-        <v>649.42</v>
+        <v>1040.35</v>
       </c>
       <c r="AB70" s="19" t="n">
-        <v>1437.12</v>
+        <v>-1142.73</v>
       </c>
       <c r="AC70" s="10" t="n"/>
       <c r="AD70" s="10" t="n"/>
@@ -16645,7 +16673,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>법인세비용차감전계속사업이익</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="E71" s="18" t="n">
@@ -16738,78 +16766,70 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>(지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="E72" s="18" t="n">
-        <v>-10634.67</v>
+        <v>-9322.51</v>
       </c>
       <c r="F72" s="9" t="n"/>
       <c r="G72" s="18" t="n">
-        <v>-2259.86</v>
+        <v>-1965.07</v>
       </c>
       <c r="H72" s="18" t="n">
-        <v>-1956.9</v>
+        <v>-1588.38</v>
       </c>
       <c r="I72" s="18" t="n">
-        <v>-1834.71</v>
+        <v>-1686.6</v>
       </c>
       <c r="J72" s="18" t="n">
-        <v>-1775.63</v>
+        <v>-1747.09</v>
       </c>
       <c r="K72" s="37" t="n">
-        <v>-7827.1</v>
+        <v>-6987.14</v>
       </c>
       <c r="L72" s="18" t="n">
-        <v>1462.43</v>
+        <v>1294.98</v>
       </c>
       <c r="M72" s="18" t="n">
-        <v>1351.76</v>
+        <v>1293.55</v>
       </c>
       <c r="N72" s="18" t="n">
-        <v>-48.81</v>
+        <v>-149</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>35.51</v>
+        <v>-102.87</v>
       </c>
       <c r="P72" s="37" t="n">
-        <v>2800.89</v>
+        <v>2336.66</v>
       </c>
       <c r="Q72" s="18" t="n">
-        <v>454.5</v>
+        <v>387.67</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>1387.4</v>
-      </c>
-      <c r="S72" s="18" t="n">
-        <v>-1488.18</v>
-      </c>
-      <c r="T72" s="18" t="n">
-        <v>-3064.22</v>
-      </c>
-      <c r="U72" s="37" t="n">
-        <v>-2710.5</v>
-      </c>
+        <v>1002.96</v>
+      </c>
+      <c r="U72" s="9" t="n"/>
       <c r="V72" s="18" t="n">
-        <v>-1786.1</v>
+        <v>-1275.7</v>
       </c>
       <c r="W72" s="18" t="n">
-        <v>-5873.93</v>
+        <v>-5231.74</v>
       </c>
       <c r="X72" s="18" t="n">
-        <v>640.89</v>
+        <v>300.02</v>
       </c>
       <c r="Y72" s="18" t="n">
-        <v>-756.9299999999999</v>
+        <v>-336.35</v>
       </c>
       <c r="Z72" s="37" t="n">
-        <v>-7776.07</v>
+        <v>-6543.77</v>
       </c>
       <c r="AA72" s="18" t="n">
-        <v>1040.35</v>
+        <v>807.87</v>
       </c>
       <c r="AB72" s="19" t="n">
-        <v>-1142.73</v>
+        <v>-258.23</v>
       </c>
       <c r="AC72" s="10" t="n"/>
       <c r="AD72" s="10" t="n"/>
@@ -16831,70 +16851,78 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>(지배주주지분)당기순이익</t>
+          <t>(비지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="E73" s="18" t="n">
-        <v>-9322.51</v>
+        <v>-1312.15</v>
       </c>
       <c r="F73" s="9" t="n"/>
       <c r="G73" s="18" t="n">
-        <v>-1965.07</v>
+        <v>-294.8</v>
       </c>
       <c r="H73" s="18" t="n">
-        <v>-1588.38</v>
+        <v>-368.52</v>
       </c>
       <c r="I73" s="18" t="n">
-        <v>-1686.6</v>
+        <v>-148.11</v>
       </c>
       <c r="J73" s="18" t="n">
-        <v>-1747.09</v>
+        <v>-28.54</v>
       </c>
       <c r="K73" s="37" t="n">
-        <v>-6987.14</v>
+        <v>-839.97</v>
       </c>
       <c r="L73" s="18" t="n">
-        <v>1294.98</v>
+        <v>167.44</v>
       </c>
       <c r="M73" s="18" t="n">
-        <v>1293.55</v>
+        <v>58.21</v>
       </c>
       <c r="N73" s="18" t="n">
-        <v>-149</v>
+        <v>100.2</v>
       </c>
       <c r="O73" s="18" t="n">
-        <v>-102.87</v>
+        <v>138.39</v>
       </c>
       <c r="P73" s="37" t="n">
-        <v>2336.66</v>
+        <v>464.24</v>
       </c>
       <c r="Q73" s="18" t="n">
-        <v>387.67</v>
+        <v>66.83</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>1002.96</v>
-      </c>
-      <c r="U73" s="9" t="n"/>
+        <v>384.44</v>
+      </c>
+      <c r="S73" s="18" t="n">
+        <v>-361.52</v>
+      </c>
+      <c r="T73" s="18" t="n">
+        <v>286.5</v>
+      </c>
+      <c r="U73" s="37" t="n">
+        <v>376.25</v>
+      </c>
       <c r="V73" s="18" t="n">
-        <v>-1275.7</v>
+        <v>-510.41</v>
       </c>
       <c r="W73" s="18" t="n">
-        <v>-5231.74</v>
+        <v>-642.1799999999999</v>
       </c>
       <c r="X73" s="18" t="n">
-        <v>300.02</v>
+        <v>340.87</v>
       </c>
       <c r="Y73" s="18" t="n">
-        <v>-336.35</v>
+        <v>-420.59</v>
       </c>
       <c r="Z73" s="37" t="n">
-        <v>-6543.77</v>
+        <v>-1232.31</v>
       </c>
       <c r="AA73" s="18" t="n">
-        <v>807.87</v>
+        <v>232.48</v>
       </c>
       <c r="AB73" s="19" t="n">
-        <v>-258.23</v>
+        <v>-884.5</v>
       </c>
       <c r="AC73" s="10" t="n"/>
       <c r="AD73" s="10" t="n"/>
@@ -16916,78 +16944,78 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>(비지배주주지분)당기순이익</t>
+          <t>총포괄손익</t>
         </is>
       </c>
       <c r="E74" s="18" t="n">
-        <v>-1312.15</v>
+        <v>-6023.73</v>
       </c>
       <c r="F74" s="9" t="n"/>
       <c r="G74" s="18" t="n">
-        <v>-294.8</v>
+        <v>-2149.5</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>-368.52</v>
+        <v>-2184.09</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>-148.11</v>
+        <v>-1836.13</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>-28.54</v>
+        <v>-1740.55</v>
       </c>
       <c r="K74" s="37" t="n">
-        <v>-839.97</v>
+        <v>-7910.27</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>167.44</v>
+        <v>1455.53</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>58.21</v>
+        <v>1356.76</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>100.2</v>
+        <v>-52.39</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>138.39</v>
+        <v>3211.25</v>
       </c>
       <c r="P74" s="37" t="n">
-        <v>464.24</v>
+        <v>5971.15</v>
       </c>
       <c r="Q74" s="18" t="n">
-        <v>66.83</v>
+        <v>454.86</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>384.44</v>
+        <v>1414.46</v>
       </c>
       <c r="S74" s="18" t="n">
-        <v>-361.52</v>
+        <v>-1514.9</v>
       </c>
       <c r="T74" s="18" t="n">
-        <v>286.5</v>
+        <v>-3280.52</v>
       </c>
       <c r="U74" s="37" t="n">
-        <v>376.25</v>
+        <v>-2926.1</v>
       </c>
       <c r="V74" s="18" t="n">
-        <v>-510.41</v>
+        <v>-1785.98</v>
       </c>
       <c r="W74" s="18" t="n">
-        <v>-642.1799999999999</v>
+        <v>-5848.68</v>
       </c>
       <c r="X74" s="18" t="n">
-        <v>340.87</v>
+        <v>665.63</v>
       </c>
       <c r="Y74" s="18" t="n">
-        <v>-420.59</v>
+        <v>-1105.24</v>
       </c>
       <c r="Z74" s="37" t="n">
-        <v>-1232.31</v>
+        <v>-8074.27</v>
       </c>
       <c r="AA74" s="18" t="n">
-        <v>232.48</v>
+        <v>1021.44</v>
       </c>
       <c r="AB74" s="19" t="n">
-        <v>-884.5</v>
+        <v>-1480.8</v>
       </c>
       <c r="AC74" s="10" t="n"/>
       <c r="AD74" s="10" t="n"/>
@@ -17009,78 +17037,78 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>총포괄손익</t>
+          <t>금융손익</t>
         </is>
       </c>
       <c r="E75" s="18" t="n">
-        <v>-6023.73</v>
+        <v>-717.34</v>
       </c>
       <c r="F75" s="9" t="n"/>
       <c r="G75" s="18" t="n">
-        <v>-2149.5</v>
+        <v>-634.09</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>-2184.09</v>
+        <v>-682.8200000000001</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>-1836.13</v>
+        <v>-698.74</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>-1740.55</v>
+        <v>-596.27</v>
       </c>
       <c r="K75" s="37" t="n">
-        <v>-7910.27</v>
+        <v>-2611.92</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>1455.53</v>
+        <v>-852.5599999999999</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>1356.76</v>
+        <v>-829.0599999999999</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>-52.39</v>
+        <v>-803.5599999999999</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>3211.25</v>
+        <v>18.02</v>
       </c>
       <c r="P75" s="37" t="n">
-        <v>5971.15</v>
+        <v>-2467.16</v>
       </c>
       <c r="Q75" s="18" t="n">
-        <v>454.86</v>
+        <v>-859.89</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>1414.46</v>
+        <v>1490.9</v>
       </c>
       <c r="S75" s="18" t="n">
-        <v>-1514.9</v>
+        <v>-1000.85</v>
       </c>
       <c r="T75" s="18" t="n">
-        <v>-3280.52</v>
+        <v>-2526.84</v>
       </c>
       <c r="U75" s="37" t="n">
-        <v>-2926.1</v>
+        <v>-2896.68</v>
       </c>
       <c r="V75" s="18" t="n">
-        <v>-1785.98</v>
+        <v>-658.3200000000001</v>
       </c>
       <c r="W75" s="18" t="n">
-        <v>-5848.68</v>
+        <v>-5387.45</v>
       </c>
       <c r="X75" s="18" t="n">
-        <v>665.63</v>
+        <v>-791.79</v>
       </c>
       <c r="Y75" s="18" t="n">
-        <v>-1105.24</v>
+        <v>-1159.28</v>
       </c>
       <c r="Z75" s="37" t="n">
-        <v>-8074.27</v>
+        <v>-7996.84</v>
       </c>
       <c r="AA75" s="18" t="n">
-        <v>1021.44</v>
+        <v>-579.17</v>
       </c>
       <c r="AB75" s="19" t="n">
-        <v>-1480.8</v>
+        <v>-1048.88</v>
       </c>
       <c r="AC75" s="10" t="n"/>
       <c r="AD75" s="10" t="n"/>
@@ -17102,78 +17130,78 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>금융손익</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="E76" s="18" t="n">
-        <v>-717.34</v>
+        <v>-4230.34</v>
       </c>
       <c r="F76" s="9" t="n"/>
       <c r="G76" s="18" t="n">
-        <v>-634.09</v>
+        <v>7.83</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>-682.8200000000001</v>
+        <v>329.43</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>-698.74</v>
+        <v>167.83</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>-596.27</v>
+        <v>-461.77</v>
       </c>
       <c r="K76" s="37" t="n">
-        <v>-2611.92</v>
+        <v>43.32</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>-852.5599999999999</v>
+        <v>130.51</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>-829.0599999999999</v>
+        <v>-86.67</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>-803.5599999999999</v>
+        <v>13.53</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>18.02</v>
+        <v>-385.8</v>
       </c>
       <c r="P76" s="37" t="n">
-        <v>-2467.16</v>
+        <v>-328.43</v>
       </c>
       <c r="Q76" s="18" t="n">
-        <v>-859.89</v>
+        <v>356.21</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>1490.9</v>
+        <v>49.9</v>
       </c>
       <c r="S76" s="18" t="n">
-        <v>-1000.85</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="T76" s="18" t="n">
-        <v>-2526.84</v>
+        <v>-751.95</v>
       </c>
       <c r="U76" s="37" t="n">
-        <v>-2896.68</v>
+        <v>-250.55</v>
       </c>
       <c r="V76" s="18" t="n">
-        <v>-658.3200000000001</v>
+        <v>39.64</v>
       </c>
       <c r="W76" s="18" t="n">
-        <v>-5387.45</v>
+        <v>-166.47</v>
       </c>
       <c r="X76" s="18" t="n">
-        <v>-791.79</v>
+        <v>260.28</v>
       </c>
       <c r="Y76" s="18" t="n">
-        <v>-1159.28</v>
+        <v>231.05</v>
       </c>
       <c r="Z76" s="37" t="n">
-        <v>-7996.84</v>
+        <v>364.5</v>
       </c>
       <c r="AA76" s="18" t="n">
-        <v>-579.17</v>
+        <v>137.47</v>
       </c>
       <c r="AB76" s="19" t="n">
-        <v>-1048.88</v>
+        <v>42.04</v>
       </c>
       <c r="AC76" s="10" t="n"/>
       <c r="AD76" s="10" t="n"/>
@@ -17195,78 +17223,78 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>계속사업이익</t>
         </is>
       </c>
       <c r="E77" s="18" t="n">
-        <v>-4230.34</v>
+        <v>-10634.67</v>
       </c>
       <c r="F77" s="9" t="n"/>
       <c r="G77" s="18" t="n">
-        <v>7.83</v>
+        <v>-2259.86</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>329.43</v>
+        <v>-1956.9</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>167.83</v>
+        <v>-1834.71</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>-461.77</v>
+        <v>-1775.63</v>
       </c>
       <c r="K77" s="37" t="n">
-        <v>43.32</v>
+        <v>-7827.1</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>130.51</v>
+        <v>1462.43</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>-86.67</v>
+        <v>1351.76</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>13.53</v>
+        <v>-48.81</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>-385.8</v>
+        <v>35.51</v>
       </c>
       <c r="P77" s="37" t="n">
-        <v>-328.43</v>
+        <v>2800.89</v>
       </c>
       <c r="Q77" s="18" t="n">
-        <v>356.21</v>
+        <v>454.5</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>49.9</v>
+        <v>1387.4</v>
       </c>
       <c r="S77" s="18" t="n">
-        <v>95.29000000000001</v>
+        <v>-1488.18</v>
       </c>
       <c r="T77" s="18" t="n">
-        <v>-751.95</v>
+        <v>-3064.22</v>
       </c>
       <c r="U77" s="37" t="n">
-        <v>-250.55</v>
+        <v>-2710.5</v>
       </c>
       <c r="V77" s="18" t="n">
-        <v>39.64</v>
+        <v>-1786.1</v>
       </c>
       <c r="W77" s="18" t="n">
-        <v>-166.47</v>
+        <v>-5873.93</v>
       </c>
       <c r="X77" s="18" t="n">
-        <v>260.28</v>
+        <v>640.89</v>
       </c>
       <c r="Y77" s="18" t="n">
-        <v>231.05</v>
+        <v>-756.9299999999999</v>
       </c>
       <c r="Z77" s="37" t="n">
-        <v>364.5</v>
+        <v>-7776.07</v>
       </c>
       <c r="AA77" s="18" t="n">
-        <v>137.47</v>
+        <v>1040.35</v>
       </c>
       <c r="AB77" s="19" t="n">
-        <v>42.04</v>
+        <v>-1142.73</v>
       </c>
       <c r="AC77" s="10" t="n"/>
       <c r="AD77" s="10" t="n"/>
@@ -17288,78 +17316,70 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>계속사업이익</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="n">
-        <v>-10634.67</v>
+          <t>법인세비용</t>
+        </is>
       </c>
       <c r="F78" s="9" t="n"/>
       <c r="G78" s="18" t="n">
-        <v>-2259.86</v>
-      </c>
-      <c r="H78" s="18" t="n">
-        <v>-1956.9</v>
+        <v>0</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>-1834.71</v>
+        <v>0</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>-1775.63</v>
-      </c>
-      <c r="K78" s="37" t="n">
-        <v>-7827.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K78" s="9" t="n"/>
       <c r="L78" s="18" t="n">
-        <v>1462.43</v>
+        <v>0</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>1351.76</v>
+        <v>0</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>-48.81</v>
+        <v>0</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>35.51</v>
+        <v>0</v>
       </c>
       <c r="P78" s="37" t="n">
-        <v>2800.89</v>
+        <v>0</v>
       </c>
       <c r="Q78" s="18" t="n">
-        <v>454.5</v>
+        <v>0</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>1387.4</v>
+        <v>0</v>
       </c>
       <c r="S78" s="18" t="n">
-        <v>-1488.18</v>
+        <v>0</v>
       </c>
       <c r="T78" s="18" t="n">
-        <v>-3064.22</v>
+        <v>0</v>
       </c>
       <c r="U78" s="37" t="n">
-        <v>-2710.5</v>
+        <v>0</v>
       </c>
       <c r="V78" s="18" t="n">
-        <v>-1786.1</v>
+        <v>0</v>
       </c>
       <c r="W78" s="18" t="n">
-        <v>-5873.93</v>
+        <v>0</v>
       </c>
       <c r="X78" s="18" t="n">
-        <v>640.89</v>
+        <v>0</v>
       </c>
       <c r="Y78" s="18" t="n">
-        <v>-756.9299999999999</v>
+        <v>0</v>
       </c>
       <c r="Z78" s="37" t="n">
-        <v>-7776.07</v>
+        <v>0</v>
       </c>
       <c r="AA78" s="18" t="n">
-        <v>1040.35</v>
+        <v>0</v>
       </c>
       <c r="AB78" s="19" t="n">
-        <v>-1142.73</v>
+        <v>0</v>
       </c>
       <c r="AC78" s="10" t="n"/>
       <c r="AD78" s="10" t="n"/>
@@ -17381,70 +17401,75 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="F79" s="9" t="n"/>
       <c r="G79" s="18" t="n">
-        <v>0</v>
+        <v>29.22</v>
+      </c>
+      <c r="H79" s="18" t="n">
+        <v>30.45</v>
       </c>
       <c r="I79" s="18" t="n">
-        <v>0</v>
+        <v>29.37</v>
       </c>
       <c r="J79" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="9" t="n"/>
+        <v>58.16</v>
+      </c>
+      <c r="K79" s="37" t="n">
+        <v>147.2</v>
+      </c>
       <c r="L79" s="18" t="n">
-        <v>0</v>
+        <v>21.79</v>
       </c>
       <c r="M79" s="18" t="n">
-        <v>0</v>
+        <v>30.87</v>
       </c>
       <c r="N79" s="18" t="n">
-        <v>0</v>
+        <v>48.41</v>
       </c>
       <c r="O79" s="18" t="n">
-        <v>0</v>
+        <v>54.11</v>
       </c>
       <c r="P79" s="37" t="n">
-        <v>0</v>
+        <v>155.18</v>
       </c>
       <c r="Q79" s="18" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="S79" s="18" t="n">
-        <v>0</v>
+        <v>22.93</v>
       </c>
       <c r="T79" s="18" t="n">
-        <v>0</v>
+        <v>66.69</v>
       </c>
       <c r="U79" s="37" t="n">
-        <v>0</v>
+        <v>104.97</v>
       </c>
       <c r="V79" s="18" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="W79" s="18" t="n">
-        <v>0</v>
+        <v>44.25</v>
       </c>
       <c r="X79" s="18" t="n">
-        <v>0</v>
+        <v>108.29</v>
       </c>
       <c r="Y79" s="18" t="n">
-        <v>0</v>
+        <v>-2.64</v>
       </c>
       <c r="Z79" s="37" t="n">
-        <v>0</v>
+        <v>157.29</v>
       </c>
       <c r="AA79" s="18" t="n">
-        <v>0</v>
+        <v>33.98</v>
       </c>
       <c r="AB79" s="19" t="n">
-        <v>0</v>
+        <v>57.55</v>
       </c>
       <c r="AC79" s="10" t="n"/>
       <c r="AD79" s="10" t="n"/>
@@ -17466,75 +17491,62 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>배당금수익</t>
         </is>
       </c>
       <c r="F80" s="9" t="n"/>
       <c r="G80" s="18" t="n">
-        <v>29.22</v>
+        <v>14.74</v>
       </c>
       <c r="H80" s="18" t="n">
-        <v>30.45</v>
+        <v>0</v>
       </c>
       <c r="I80" s="18" t="n">
-        <v>29.37</v>
+        <v>0</v>
       </c>
       <c r="J80" s="18" t="n">
-        <v>58.16</v>
+        <v>0</v>
       </c>
       <c r="K80" s="37" t="n">
-        <v>147.2</v>
-      </c>
-      <c r="L80" s="18" t="n">
-        <v>21.79</v>
+        <v>14.74</v>
       </c>
       <c r="M80" s="18" t="n">
-        <v>30.87</v>
+        <v>6.7</v>
       </c>
       <c r="N80" s="18" t="n">
-        <v>48.41</v>
+        <v>35.14</v>
       </c>
       <c r="O80" s="18" t="n">
-        <v>54.11</v>
-      </c>
-      <c r="P80" s="37" t="n">
-        <v>155.18</v>
-      </c>
-      <c r="Q80" s="18" t="n">
-        <v>8.25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P80" s="9" t="n"/>
       <c r="R80" s="18" t="n">
-        <v>7.1</v>
+        <v>113.34</v>
       </c>
       <c r="S80" s="18" t="n">
-        <v>22.93</v>
+        <v>81.2</v>
       </c>
       <c r="T80" s="18" t="n">
-        <v>66.69</v>
-      </c>
-      <c r="U80" s="37" t="n">
-        <v>104.97</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U80" s="9" t="n"/>
       <c r="V80" s="18" t="n">
-        <v>7.39</v>
+        <v>161</v>
       </c>
       <c r="W80" s="18" t="n">
-        <v>44.25</v>
+        <v>15.2</v>
       </c>
       <c r="X80" s="18" t="n">
-        <v>108.29</v>
+        <v>0</v>
       </c>
       <c r="Y80" s="18" t="n">
-        <v>-2.64</v>
+        <v>120.4</v>
       </c>
       <c r="Z80" s="37" t="n">
-        <v>157.29</v>
-      </c>
-      <c r="AA80" s="18" t="n">
-        <v>33.98</v>
+        <v>296.6</v>
       </c>
       <c r="AB80" s="19" t="n">
-        <v>57.55</v>
+        <v>182.2</v>
       </c>
       <c r="AC80" s="10" t="n"/>
       <c r="AD80" s="10" t="n"/>
@@ -17556,62 +17568,75 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>배당금수익</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="F81" s="9" t="n"/>
       <c r="G81" s="18" t="n">
-        <v>14.74</v>
+        <v>677.95</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>0</v>
+        <v>716.74</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>0</v>
+        <v>744.54</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>0</v>
+        <v>856.08</v>
       </c>
       <c r="K81" s="37" t="n">
-        <v>14.74</v>
+        <v>2995.31</v>
+      </c>
+      <c r="L81" s="18" t="n">
+        <v>875.61</v>
       </c>
       <c r="M81" s="18" t="n">
-        <v>6.7</v>
+        <v>858.4</v>
       </c>
       <c r="N81" s="18" t="n">
-        <v>35.14</v>
+        <v>878.9400000000001</v>
       </c>
       <c r="O81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" s="9" t="n"/>
+        <v>1020.25</v>
+      </c>
+      <c r="P81" s="37" t="n">
+        <v>3633.2</v>
+      </c>
+      <c r="Q81" s="18" t="n">
+        <v>871.54</v>
+      </c>
       <c r="R81" s="18" t="n">
-        <v>113.34</v>
+        <v>1476.73</v>
       </c>
       <c r="S81" s="18" t="n">
-        <v>81.2</v>
+        <v>1091.19</v>
       </c>
       <c r="T81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" s="9" t="n"/>
+        <v>1398.26</v>
+      </c>
+      <c r="U81" s="37" t="n">
+        <v>4837.72</v>
+      </c>
       <c r="V81" s="18" t="n">
-        <v>161</v>
+        <v>830.12</v>
       </c>
       <c r="W81" s="18" t="n">
-        <v>15.2</v>
+        <v>1522.14</v>
       </c>
       <c r="X81" s="18" t="n">
-        <v>0</v>
+        <v>324.01</v>
       </c>
       <c r="Y81" s="18" t="n">
-        <v>120.4</v>
+        <v>806.59</v>
       </c>
       <c r="Z81" s="37" t="n">
-        <v>296.6</v>
+        <v>3482.86</v>
+      </c>
+      <c r="AA81" s="18" t="n">
+        <v>644.47</v>
       </c>
       <c r="AB81" s="19" t="n">
-        <v>182.2</v>
+        <v>1224.09</v>
       </c>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
@@ -17633,75 +17658,70 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>외환차익</t>
         </is>
       </c>
       <c r="F82" s="9" t="n"/>
       <c r="G82" s="18" t="n">
-        <v>677.95</v>
+        <v>1.78</v>
       </c>
       <c r="H82" s="18" t="n">
-        <v>716.74</v>
+        <v>2.94</v>
       </c>
       <c r="I82" s="18" t="n">
-        <v>744.54</v>
+        <v>11.36</v>
       </c>
       <c r="J82" s="18" t="n">
-        <v>856.08</v>
+        <v>-9.57</v>
       </c>
       <c r="K82" s="37" t="n">
-        <v>2995.31</v>
+        <v>6.51</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>875.61</v>
+        <v>1.04</v>
       </c>
       <c r="M82" s="18" t="n">
-        <v>858.4</v>
+        <v>0.34</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>878.9400000000001</v>
+        <v>-4.98</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>1020.25</v>
+        <v>2.62</v>
       </c>
       <c r="P82" s="37" t="n">
-        <v>3633.2</v>
+        <v>-0.98</v>
       </c>
       <c r="Q82" s="18" t="n">
-        <v>871.54</v>
+        <v>0.49</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>1476.73</v>
+        <v>0.22</v>
       </c>
       <c r="S82" s="18" t="n">
-        <v>1091.19</v>
+        <v>0</v>
       </c>
       <c r="T82" s="18" t="n">
-        <v>1398.26</v>
+        <v>0.23</v>
       </c>
       <c r="U82" s="37" t="n">
-        <v>4837.72</v>
-      </c>
-      <c r="V82" s="18" t="n">
-        <v>830.12</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="W82" s="18" t="n">
-        <v>1522.14</v>
+        <v>67.86</v>
       </c>
       <c r="X82" s="18" t="n">
-        <v>324.01</v>
+        <v>0.98</v>
       </c>
       <c r="Y82" s="18" t="n">
-        <v>806.59</v>
-      </c>
-      <c r="Z82" s="37" t="n">
-        <v>3482.86</v>
-      </c>
+        <v>48.28</v>
+      </c>
+      <c r="Z82" s="9" t="n"/>
       <c r="AA82" s="18" t="n">
-        <v>644.47</v>
+        <v>32.79</v>
       </c>
       <c r="AB82" s="19" t="n">
-        <v>1224.09</v>
+        <v>3.43</v>
       </c>
       <c r="AC82" s="10" t="n"/>
       <c r="AD82" s="10" t="n"/>
@@ -17723,70 +17743,51 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>외환차익</t>
+          <t>외화환산손실</t>
         </is>
       </c>
       <c r="F83" s="9" t="n"/>
       <c r="G83" s="18" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="H83" s="18" t="n">
-        <v>2.94</v>
+        <v>-1.18</v>
       </c>
       <c r="I83" s="18" t="n">
-        <v>11.36</v>
-      </c>
-      <c r="J83" s="18" t="n">
-        <v>-9.57</v>
-      </c>
-      <c r="K83" s="37" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="L83" s="18" t="n">
-        <v>1.04</v>
-      </c>
+        <v>-0.7</v>
+      </c>
+      <c r="K83" s="9" t="n"/>
       <c r="M83" s="18" t="n">
-        <v>0.34</v>
+        <v>0.84</v>
       </c>
       <c r="N83" s="18" t="n">
-        <v>-4.98</v>
+        <v>0.19</v>
       </c>
       <c r="O83" s="18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P83" s="37" t="n">
-        <v>-0.98</v>
-      </c>
+        <v>2.33</v>
+      </c>
+      <c r="P83" s="9" t="n"/>
       <c r="Q83" s="18" t="n">
-        <v>0.49</v>
+        <v>3.67</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>0.22</v>
+        <v>0.9</v>
       </c>
       <c r="S83" s="18" t="n">
-        <v>0</v>
+        <v>9.59</v>
       </c>
       <c r="T83" s="18" t="n">
-        <v>0.23</v>
+        <v>-7.95</v>
       </c>
       <c r="U83" s="37" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="W83" s="18" t="n">
-        <v>67.86</v>
-      </c>
-      <c r="X83" s="18" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="Y83" s="18" t="n">
-        <v>48.28</v>
+        <v>6.21</v>
       </c>
       <c r="Z83" s="9" t="n"/>
       <c r="AA83" s="18" t="n">
-        <v>32.79</v>
+        <v>-4.95</v>
       </c>
       <c r="AB83" s="19" t="n">
-        <v>3.43</v>
+        <v>4.95</v>
       </c>
       <c r="AC83" s="10" t="n"/>
       <c r="AD83" s="10" t="n"/>
@@ -17808,51 +17809,75 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>외화환산손실</t>
+          <t>이자손익</t>
         </is>
       </c>
       <c r="F84" s="9" t="n"/>
       <c r="G84" s="18" t="n">
-        <v>1.87</v>
+        <v>-648.73</v>
       </c>
       <c r="H84" s="18" t="n">
-        <v>-1.18</v>
+        <v>-686.29</v>
       </c>
       <c r="I84" s="18" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="K84" s="9" t="n"/>
+        <v>-715.17</v>
+      </c>
+      <c r="J84" s="18" t="n">
+        <v>-797.92</v>
+      </c>
+      <c r="K84" s="37" t="n">
+        <v>-2848.11</v>
+      </c>
+      <c r="L84" s="18" t="n">
+        <v>-853.8200000000001</v>
+      </c>
       <c r="M84" s="18" t="n">
-        <v>0.84</v>
+        <v>-827.53</v>
       </c>
       <c r="N84" s="18" t="n">
-        <v>0.19</v>
+        <v>-830.53</v>
       </c>
       <c r="O84" s="18" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="P84" s="9" t="n"/>
+        <v>-966.14</v>
+      </c>
+      <c r="P84" s="37" t="n">
+        <v>-3478.02</v>
+      </c>
       <c r="Q84" s="18" t="n">
-        <v>3.67</v>
+        <v>-863.29</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>0.9</v>
+        <v>-1469.63</v>
       </c>
       <c r="S84" s="18" t="n">
-        <v>9.59</v>
+        <v>-1068.26</v>
       </c>
       <c r="T84" s="18" t="n">
-        <v>-7.95</v>
+        <v>-1331.57</v>
       </c>
       <c r="U84" s="37" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="Z84" s="9" t="n"/>
+        <v>-4732.75</v>
+      </c>
+      <c r="V84" s="18" t="n">
+        <v>-822.73</v>
+      </c>
+      <c r="W84" s="18" t="n">
+        <v>-1477.89</v>
+      </c>
+      <c r="X84" s="18" t="n">
+        <v>-215.72</v>
+      </c>
+      <c r="Y84" s="18" t="n">
+        <v>-809.23</v>
+      </c>
+      <c r="Z84" s="37" t="n">
+        <v>-3325.57</v>
+      </c>
       <c r="AA84" s="18" t="n">
-        <v>-4.95</v>
+        <v>-610.49</v>
       </c>
       <c r="AB84" s="19" t="n">
-        <v>4.95</v>
+        <v>-1166.54</v>
       </c>
       <c r="AC84" s="10" t="n"/>
       <c r="AD84" s="10" t="n"/>
@@ -17874,75 +17899,60 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>이자손익</t>
+          <t>외환차손</t>
         </is>
       </c>
       <c r="F85" s="9" t="n"/>
-      <c r="G85" s="18" t="n">
-        <v>-648.73</v>
-      </c>
       <c r="H85" s="18" t="n">
-        <v>-686.29</v>
+        <v>2.42</v>
       </c>
       <c r="I85" s="18" t="n">
-        <v>-715.17</v>
+        <v>1.12</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>-797.92</v>
-      </c>
-      <c r="K85" s="37" t="n">
-        <v>-2848.11</v>
-      </c>
+        <v>32.92</v>
+      </c>
+      <c r="K85" s="9" t="n"/>
       <c r="L85" s="18" t="n">
-        <v>-853.8200000000001</v>
+        <v>1.37</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>-827.53</v>
+        <v>7.55</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>-830.53</v>
+        <v>1.4</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>-966.14</v>
+        <v>0.53</v>
       </c>
       <c r="P85" s="37" t="n">
-        <v>-3478.02</v>
-      </c>
-      <c r="Q85" s="18" t="n">
-        <v>-863.29</v>
+        <v>10.85</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>-1469.63</v>
+        <v>1.26</v>
       </c>
       <c r="S85" s="18" t="n">
-        <v>-1068.26</v>
+        <v>0</v>
       </c>
       <c r="T85" s="18" t="n">
-        <v>-1331.57</v>
-      </c>
-      <c r="U85" s="37" t="n">
-        <v>-4732.75</v>
-      </c>
-      <c r="V85" s="18" t="n">
-        <v>-822.73</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U85" s="9" t="n"/>
       <c r="W85" s="18" t="n">
-        <v>-1477.89</v>
+        <v>20.27</v>
       </c>
       <c r="X85" s="18" t="n">
-        <v>-215.72</v>
+        <v>1.61</v>
       </c>
       <c r="Y85" s="18" t="n">
-        <v>-809.23</v>
-      </c>
-      <c r="Z85" s="37" t="n">
-        <v>-3325.57</v>
-      </c>
+        <v>5.73</v>
+      </c>
+      <c r="Z85" s="9" t="n"/>
       <c r="AA85" s="18" t="n">
-        <v>-610.49</v>
+        <v>2.77</v>
       </c>
       <c r="AB85" s="19" t="n">
-        <v>-1166.54</v>
+        <v>1.69</v>
       </c>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
@@ -17964,60 +17974,45 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>외환차손</t>
+          <t>외화환산이익</t>
         </is>
       </c>
       <c r="F86" s="9" t="n"/>
       <c r="H86" s="18" t="n">
-        <v>2.42</v>
+        <v>0.64</v>
       </c>
       <c r="I86" s="18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="J86" s="18" t="n">
-        <v>32.92</v>
+        <v>5.5</v>
       </c>
       <c r="K86" s="9" t="n"/>
       <c r="L86" s="18" t="n">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="M86" s="18" t="n">
-        <v>7.55</v>
+        <v>-1.38</v>
       </c>
       <c r="N86" s="18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O86" s="18" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="P86" s="37" t="n">
-        <v>10.85</v>
+        <v>-1.38</v>
+      </c>
+      <c r="P86" s="9" t="n"/>
+      <c r="Q86" s="18" t="n">
+        <v>6.59</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>1.26</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="S86" s="18" t="n">
-        <v>0</v>
+        <v>-4.19</v>
       </c>
       <c r="T86" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U86" s="9" t="n"/>
-      <c r="W86" s="18" t="n">
-        <v>20.27</v>
-      </c>
-      <c r="X86" s="18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Y86" s="18" t="n">
-        <v>5.73</v>
+        <v>47.34</v>
+      </c>
+      <c r="U86" s="37" t="n">
+        <v>59.19</v>
       </c>
       <c r="Z86" s="9" t="n"/>
-      <c r="AA86" s="18" t="n">
-        <v>2.77</v>
-      </c>
       <c r="AB86" s="19" t="n">
-        <v>1.69</v>
+        <v>104.28</v>
       </c>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
@@ -18039,46 +18034,33 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>외화환산이익</t>
+          <t>파생상품이익</t>
         </is>
       </c>
       <c r="F87" s="9" t="n"/>
-      <c r="H87" s="18" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I87" s="18" t="n">
-        <v>5.5</v>
-      </c>
       <c r="K87" s="9" t="n"/>
-      <c r="L87" s="18" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="M87" s="18" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="N87" s="18" t="n">
-        <v>-1.38</v>
-      </c>
       <c r="P87" s="9" t="n"/>
-      <c r="Q87" s="18" t="n">
-        <v>6.59</v>
-      </c>
       <c r="R87" s="18" t="n">
-        <v>9.449999999999999</v>
+        <v>2895.66</v>
       </c>
       <c r="S87" s="18" t="n">
-        <v>-4.19</v>
+        <v>2895.66</v>
       </c>
       <c r="T87" s="18" t="n">
-        <v>47.34</v>
-      </c>
-      <c r="U87" s="37" t="n">
-        <v>59.19</v>
+        <v>-942.02</v>
+      </c>
+      <c r="U87" s="9" t="n"/>
+      <c r="W87" s="18" t="n">
+        <v>1585.89</v>
+      </c>
+      <c r="X87" s="18" t="n">
+        <v>1853.27</v>
+      </c>
+      <c r="Y87" s="18" t="n">
+        <v>-646.64</v>
       </c>
       <c r="Z87" s="9" t="n"/>
-      <c r="AB87" s="19" t="n">
-        <v>104.28</v>
-      </c>
+      <c r="AB87" s="5" t="n"/>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
       <c r="AE87" s="11" t="n"/>
@@ -18099,33 +18081,35 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>파생상품이익</t>
+          <t>파생상품손실</t>
         </is>
       </c>
       <c r="F88" s="9" t="n"/>
       <c r="K88" s="9" t="n"/>
       <c r="P88" s="9" t="n"/>
       <c r="R88" s="18" t="n">
-        <v>2895.66</v>
+        <v>57.17</v>
       </c>
       <c r="S88" s="18" t="n">
-        <v>2895.66</v>
+        <v>57.17</v>
       </c>
       <c r="T88" s="18" t="n">
-        <v>-942.02</v>
+        <v>318.04</v>
       </c>
       <c r="U88" s="9" t="n"/>
       <c r="W88" s="18" t="n">
-        <v>1585.89</v>
+        <v>5561.59</v>
       </c>
       <c r="X88" s="18" t="n">
-        <v>1853.27</v>
+        <v>1840.41</v>
       </c>
       <c r="Y88" s="18" t="n">
-        <v>-646.64</v>
+        <v>-146.22</v>
       </c>
       <c r="Z88" s="9" t="n"/>
-      <c r="AB88" s="5" t="n"/>
+      <c r="AB88" s="19" t="n">
+        <v>211.04</v>
+      </c>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
       <c r="AE88" s="11" t="n"/>
@@ -18146,34 +18130,78 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>파생상품손실</t>
-        </is>
+          <t>영업활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E89" s="18" t="n">
+        <v>1204.04</v>
       </c>
       <c r="F89" s="9" t="n"/>
-      <c r="K89" s="9" t="n"/>
-      <c r="P89" s="9" t="n"/>
+      <c r="G89" s="18" t="n">
+        <v>-3916.87</v>
+      </c>
+      <c r="H89" s="18" t="n">
+        <v>-1857.46</v>
+      </c>
+      <c r="I89" s="18" t="n">
+        <v>712.87</v>
+      </c>
+      <c r="J89" s="18" t="n">
+        <v>2108.14</v>
+      </c>
+      <c r="K89" s="37" t="n">
+        <v>-2953.32</v>
+      </c>
+      <c r="L89" s="18" t="n">
+        <v>1738.04</v>
+      </c>
+      <c r="M89" s="18" t="n">
+        <v>2891.62</v>
+      </c>
+      <c r="N89" s="18" t="n">
+        <v>631.15</v>
+      </c>
+      <c r="O89" s="18" t="n">
+        <v>-5824.89</v>
+      </c>
+      <c r="P89" s="37" t="n">
+        <v>-564.08</v>
+      </c>
+      <c r="Q89" s="18" t="n">
+        <v>-3168.15</v>
+      </c>
       <c r="R89" s="18" t="n">
-        <v>57.17</v>
+        <v>-3013.06</v>
       </c>
       <c r="S89" s="18" t="n">
-        <v>57.17</v>
+        <v>-897.4400000000001</v>
       </c>
       <c r="T89" s="18" t="n">
-        <v>318.04</v>
-      </c>
-      <c r="U89" s="9" t="n"/>
+        <v>769.01</v>
+      </c>
+      <c r="U89" s="37" t="n">
+        <v>-6309.64</v>
+      </c>
+      <c r="V89" s="18" t="n">
+        <v>-2764.95</v>
+      </c>
       <c r="W89" s="18" t="n">
-        <v>5561.59</v>
+        <v>-2011.11</v>
       </c>
       <c r="X89" s="18" t="n">
-        <v>1840.41</v>
+        <v>5045.41</v>
       </c>
       <c r="Y89" s="18" t="n">
-        <v>-146.22</v>
-      </c>
-      <c r="Z89" s="9" t="n"/>
+        <v>-4762.46</v>
+      </c>
+      <c r="Z89" s="37" t="n">
+        <v>-4493.11</v>
+      </c>
+      <c r="AA89" s="18" t="n">
+        <v>-86.09999999999999</v>
+      </c>
       <c r="AB89" s="19" t="n">
-        <v>211.04</v>
+        <v>3483.46</v>
       </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
@@ -18195,79 +18223,38 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="E90" s="18" t="n">
-        <v>1204.04</v>
+        <v>452.45</v>
       </c>
       <c r="F90" s="9" t="n"/>
       <c r="G90" s="18" t="n">
-        <v>-3916.87</v>
+        <v>269.04</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>-1857.46</v>
+        <v>299.44</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>712.87</v>
+        <v>237.14</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>2108.14</v>
+        <v>273.15</v>
       </c>
       <c r="K90" s="37" t="n">
-        <v>-2953.32</v>
+        <v>1078.77</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>1738.04</v>
+        <v>234.26</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>2891.62</v>
-      </c>
-      <c r="N90" s="18" t="n">
-        <v>631.15</v>
-      </c>
-      <c r="O90" s="18" t="n">
-        <v>-5824.89</v>
-      </c>
-      <c r="P90" s="37" t="n">
-        <v>-564.08</v>
-      </c>
-      <c r="Q90" s="18" t="n">
-        <v>-3168.15</v>
-      </c>
-      <c r="R90" s="18" t="n">
-        <v>-3013.06</v>
-      </c>
-      <c r="S90" s="18" t="n">
-        <v>-897.4400000000001</v>
-      </c>
-      <c r="T90" s="18" t="n">
-        <v>769.01</v>
-      </c>
-      <c r="U90" s="37" t="n">
-        <v>-6309.64</v>
-      </c>
-      <c r="V90" s="18" t="n">
-        <v>-2764.95</v>
-      </c>
-      <c r="W90" s="18" t="n">
-        <v>-2011.11</v>
-      </c>
-      <c r="X90" s="18" t="n">
-        <v>5045.41</v>
-      </c>
-      <c r="Y90" s="18" t="n">
-        <v>-4762.46</v>
-      </c>
-      <c r="Z90" s="37" t="n">
-        <v>-4493.11</v>
-      </c>
-      <c r="AA90" s="18" t="n">
-        <v>-86.09999999999999</v>
-      </c>
-      <c r="AB90" s="19" t="n">
-        <v>3483.46</v>
-      </c>
+        <v>278.7</v>
+      </c>
+      <c r="P90" s="9" t="n"/>
+      <c r="U90" s="9" t="n"/>
+      <c r="Z90" s="9" t="n"/>
+      <c r="AB90" s="5" t="n"/>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
       <c r="AE90" s="11" t="n"/>
@@ -18288,33 +18275,33 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>무형자산상각비</t>
         </is>
       </c>
       <c r="E91" s="18" t="n">
-        <v>452.45</v>
+        <v>24.79</v>
       </c>
       <c r="F91" s="9" t="n"/>
       <c r="G91" s="18" t="n">
-        <v>269.04</v>
+        <v>3.36</v>
       </c>
       <c r="H91" s="18" t="n">
-        <v>299.44</v>
+        <v>3.37</v>
       </c>
       <c r="I91" s="18" t="n">
-        <v>237.14</v>
+        <v>3.36</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>273.15</v>
+        <v>0.27</v>
       </c>
       <c r="K91" s="37" t="n">
-        <v>1078.77</v>
+        <v>10.36</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>234.26</v>
+        <v>0.27</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>278.7</v>
+        <v>1.7</v>
       </c>
       <c r="P91" s="9" t="n"/>
       <c r="U91" s="9" t="n"/>
@@ -18340,38 +18327,79 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>무형자산상각비</t>
+          <t>배당금수취(CF)</t>
         </is>
       </c>
       <c r="E92" s="18" t="n">
-        <v>24.79</v>
+        <v>0</v>
       </c>
       <c r="F92" s="9" t="n"/>
       <c r="G92" s="18" t="n">
-        <v>3.36</v>
+        <v>14.74</v>
       </c>
       <c r="H92" s="18" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="I92" s="18" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="J92" s="18" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="K92" s="37" t="n">
-        <v>10.36</v>
+        <v>14.74</v>
       </c>
       <c r="L92" s="18" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="M92" s="18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P92" s="9" t="n"/>
-      <c r="U92" s="9" t="n"/>
-      <c r="Z92" s="9" t="n"/>
-      <c r="AB92" s="5" t="n"/>
+        <v>6.7</v>
+      </c>
+      <c r="N92" s="18" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="O92" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" s="37" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="Q92" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" s="18" t="n">
+        <v>113.34</v>
+      </c>
+      <c r="S92" s="18" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="T92" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" s="37" t="n">
+        <v>194.54</v>
+      </c>
+      <c r="V92" s="18" t="n">
+        <v>161</v>
+      </c>
+      <c r="W92" s="18" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="X92" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="18" t="n">
+        <v>120.4</v>
+      </c>
+      <c r="Z92" s="37" t="n">
+        <v>296.6</v>
+      </c>
+      <c r="AA92" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="19" t="n">
+        <v>182.2</v>
+      </c>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
       <c r="AE92" s="11" t="n"/>
@@ -18392,78 +18420,78 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E93" s="18" t="n">
-        <v>0</v>
+        <v>-0.83</v>
       </c>
       <c r="F93" s="9" t="n"/>
       <c r="G93" s="18" t="n">
-        <v>14.74</v>
+        <v>-0.52</v>
       </c>
       <c r="H93" s="18" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="I93" s="18" t="n">
-        <v>0</v>
+        <v>61.72</v>
       </c>
       <c r="J93" s="18" t="n">
-        <v>0</v>
+        <v>-1.82</v>
       </c>
       <c r="K93" s="37" t="n">
-        <v>14.74</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L93" s="18" t="n">
-        <v>0</v>
+        <v>-0.97</v>
       </c>
       <c r="M93" s="18" t="n">
-        <v>6.7</v>
+        <v>1.87</v>
       </c>
       <c r="N93" s="18" t="n">
-        <v>50.4</v>
+        <v>-1.07</v>
       </c>
       <c r="O93" s="18" t="n">
-        <v>0</v>
+        <v>-7.32</v>
       </c>
       <c r="P93" s="37" t="n">
-        <v>57.1</v>
+        <v>-7.49</v>
       </c>
       <c r="Q93" s="18" t="n">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>113.34</v>
+        <v>7.19</v>
       </c>
       <c r="S93" s="18" t="n">
-        <v>81.2</v>
+        <v>-0.73</v>
       </c>
       <c r="T93" s="18" t="n">
-        <v>0</v>
+        <v>-10.68</v>
       </c>
       <c r="U93" s="37" t="n">
-        <v>194.54</v>
+        <v>-4.57</v>
       </c>
       <c r="V93" s="18" t="n">
-        <v>161</v>
+        <v>-1.85</v>
       </c>
       <c r="W93" s="18" t="n">
-        <v>15.2</v>
+        <v>12.19</v>
       </c>
       <c r="X93" s="18" t="n">
-        <v>0</v>
+        <v>-59.16</v>
       </c>
       <c r="Y93" s="18" t="n">
-        <v>120.4</v>
+        <v>-0.65</v>
       </c>
       <c r="Z93" s="37" t="n">
-        <v>296.6</v>
+        <v>-49.47</v>
       </c>
       <c r="AA93" s="18" t="n">
-        <v>0</v>
+        <v>-0.88</v>
       </c>
       <c r="AB93" s="19" t="n">
-        <v>182.2</v>
+        <v>59.58</v>
       </c>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
@@ -18485,78 +18513,78 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E94" s="18" t="n">
-        <v>-0.83</v>
+        <v>1469.41</v>
       </c>
       <c r="F94" s="9" t="n"/>
       <c r="G94" s="18" t="n">
-        <v>-0.52</v>
+        <v>-1151.52</v>
       </c>
       <c r="H94" s="18" t="n">
-        <v>5.63</v>
+        <v>2441.13</v>
       </c>
       <c r="I94" s="18" t="n">
-        <v>61.72</v>
+        <v>-349.97</v>
       </c>
       <c r="J94" s="18" t="n">
-        <v>-1.82</v>
+        <v>-146.34</v>
       </c>
       <c r="K94" s="37" t="n">
-        <v>65.01000000000001</v>
+        <v>793.3</v>
       </c>
       <c r="L94" s="18" t="n">
-        <v>-0.97</v>
+        <v>390.06</v>
       </c>
       <c r="M94" s="18" t="n">
-        <v>1.87</v>
+        <v>-1714.7</v>
       </c>
       <c r="N94" s="18" t="n">
-        <v>-1.07</v>
+        <v>-1408.6</v>
       </c>
       <c r="O94" s="18" t="n">
-        <v>-7.32</v>
+        <v>1727.97</v>
       </c>
       <c r="P94" s="37" t="n">
-        <v>-7.49</v>
+        <v>-1005.27</v>
       </c>
       <c r="Q94" s="18" t="n">
-        <v>-0.35</v>
+        <v>425.48</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>7.19</v>
+        <v>-492.97</v>
       </c>
       <c r="S94" s="18" t="n">
-        <v>-0.73</v>
+        <v>540.1900000000001</v>
       </c>
       <c r="T94" s="18" t="n">
-        <v>-10.68</v>
+        <v>-722.91</v>
       </c>
       <c r="U94" s="37" t="n">
-        <v>-4.57</v>
+        <v>-250.21</v>
       </c>
       <c r="V94" s="18" t="n">
-        <v>-1.85</v>
+        <v>971.0599999999999</v>
       </c>
       <c r="W94" s="18" t="n">
-        <v>12.19</v>
+        <v>398.57</v>
       </c>
       <c r="X94" s="18" t="n">
-        <v>-59.16</v>
+        <v>62.12</v>
       </c>
       <c r="Y94" s="18" t="n">
-        <v>-0.65</v>
+        <v>-2480.92</v>
       </c>
       <c r="Z94" s="37" t="n">
-        <v>-49.47</v>
+        <v>-1049.17</v>
       </c>
       <c r="AA94" s="18" t="n">
-        <v>-0.88</v>
+        <v>-229.4</v>
       </c>
       <c r="AB94" s="19" t="n">
-        <v>59.58</v>
+        <v>-204.39</v>
       </c>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
@@ -18578,78 +18606,78 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="E95" s="18" t="n">
-        <v>1469.41</v>
+        <v>0</v>
       </c>
       <c r="F95" s="9" t="n"/>
       <c r="G95" s="18" t="n">
-        <v>-1151.52</v>
+        <v>0</v>
       </c>
       <c r="H95" s="18" t="n">
-        <v>2441.13</v>
+        <v>0</v>
       </c>
       <c r="I95" s="18" t="n">
-        <v>-349.97</v>
+        <v>5</v>
       </c>
       <c r="J95" s="18" t="n">
-        <v>-146.34</v>
+        <v>158.07</v>
       </c>
       <c r="K95" s="37" t="n">
-        <v>793.3</v>
+        <v>163.07</v>
       </c>
       <c r="L95" s="18" t="n">
-        <v>390.06</v>
+        <v>4.5</v>
       </c>
       <c r="M95" s="18" t="n">
-        <v>-1714.7</v>
+        <v>0</v>
       </c>
       <c r="N95" s="18" t="n">
-        <v>-1408.6</v>
+        <v>0</v>
       </c>
       <c r="O95" s="18" t="n">
-        <v>1727.97</v>
+        <v>1</v>
       </c>
       <c r="P95" s="37" t="n">
-        <v>-1005.27</v>
+        <v>5.5</v>
       </c>
       <c r="Q95" s="18" t="n">
-        <v>425.48</v>
+        <v>9.27</v>
       </c>
       <c r="R95" s="18" t="n">
-        <v>-492.97</v>
+        <v>3.82</v>
       </c>
       <c r="S95" s="18" t="n">
-        <v>540.1900000000001</v>
+        <v>0.64</v>
       </c>
       <c r="T95" s="18" t="n">
-        <v>-722.91</v>
+        <v>9</v>
       </c>
       <c r="U95" s="37" t="n">
-        <v>-250.21</v>
+        <v>22.73</v>
       </c>
       <c r="V95" s="18" t="n">
-        <v>971.0599999999999</v>
+        <v>0</v>
       </c>
       <c r="W95" s="18" t="n">
-        <v>398.57</v>
+        <v>0</v>
       </c>
       <c r="X95" s="18" t="n">
-        <v>62.12</v>
+        <v>0</v>
       </c>
       <c r="Y95" s="18" t="n">
-        <v>-2480.92</v>
+        <v>1</v>
       </c>
       <c r="Z95" s="37" t="n">
-        <v>-1049.17</v>
+        <v>1</v>
       </c>
       <c r="AA95" s="18" t="n">
-        <v>-229.4</v>
+        <v>25.91</v>
       </c>
       <c r="AB95" s="19" t="n">
-        <v>-204.39</v>
+        <v>11.16</v>
       </c>
       <c r="AC95" s="10" t="n"/>
       <c r="AD95" s="10" t="n"/>
@@ -18671,11 +18699,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E96" s="18" t="n">
-        <v>0</v>
+        <v>31.93</v>
       </c>
       <c r="F96" s="9" t="n"/>
       <c r="G96" s="18" t="n">
@@ -18685,64 +18713,54 @@
         <v>0</v>
       </c>
       <c r="I96" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="J96" s="18" t="n">
-        <v>158.07</v>
-      </c>
-      <c r="K96" s="37" t="n">
-        <v>163.07</v>
-      </c>
+        <v>115.01</v>
+      </c>
+      <c r="K96" s="9" t="n"/>
       <c r="L96" s="18" t="n">
-        <v>4.5</v>
+        <v>140.98</v>
       </c>
       <c r="M96" s="18" t="n">
-        <v>0</v>
+        <v>56.42</v>
       </c>
       <c r="N96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P96" s="37" t="n">
-        <v>5.5</v>
-      </c>
+        <v>326.86</v>
+      </c>
+      <c r="P96" s="9" t="n"/>
       <c r="Q96" s="18" t="n">
-        <v>9.27</v>
+        <v>96.36</v>
       </c>
       <c r="R96" s="18" t="n">
-        <v>3.82</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="S96" s="18" t="n">
-        <v>0.64</v>
+        <v>76.8</v>
       </c>
       <c r="T96" s="18" t="n">
-        <v>9</v>
+        <v>153.62</v>
       </c>
       <c r="U96" s="37" t="n">
-        <v>22.73</v>
+        <v>394.93</v>
       </c>
       <c r="V96" s="18" t="n">
-        <v>0</v>
+        <v>113.19</v>
       </c>
       <c r="W96" s="18" t="n">
-        <v>0</v>
+        <v>42.76</v>
       </c>
       <c r="X96" s="18" t="n">
-        <v>0</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="Y96" s="18" t="n">
-        <v>1</v>
+        <v>497.93</v>
       </c>
       <c r="Z96" s="37" t="n">
-        <v>1</v>
+        <v>738.87</v>
       </c>
       <c r="AA96" s="18" t="n">
-        <v>25.91</v>
+        <v>146.42</v>
       </c>
       <c r="AB96" s="19" t="n">
-        <v>11.16</v>
+        <v>38.01</v>
       </c>
       <c r="AC96" s="10" t="n"/>
       <c r="AD96" s="10" t="n"/>
@@ -18764,7 +18782,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="E97" s="18" t="n">
@@ -18780,19 +18798,29 @@
       <c r="I97" s="18" t="n">
         <v>115.01</v>
       </c>
-      <c r="K97" s="9" t="n"/>
+      <c r="J97" s="18" t="n">
+        <v>71.09</v>
+      </c>
+      <c r="K97" s="37" t="n">
+        <v>186.1</v>
+      </c>
       <c r="L97" s="18" t="n">
         <v>140.98</v>
       </c>
       <c r="M97" s="18" t="n">
-        <v>56.42</v>
+        <v>84.98</v>
       </c>
       <c r="N97" s="18" t="n">
-        <v>326.86</v>
-      </c>
-      <c r="P97" s="9" t="n"/>
+        <v>333.86</v>
+      </c>
+      <c r="O97" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" s="37" t="n">
+        <v>559.8200000000001</v>
+      </c>
       <c r="Q97" s="18" t="n">
-        <v>96.36</v>
+        <v>103.39</v>
       </c>
       <c r="R97" s="18" t="n">
         <v>68.15000000000001</v>
@@ -18804,28 +18832,28 @@
         <v>153.62</v>
       </c>
       <c r="U97" s="37" t="n">
-        <v>394.93</v>
+        <v>401.96</v>
       </c>
       <c r="V97" s="18" t="n">
         <v>113.19</v>
       </c>
       <c r="W97" s="18" t="n">
-        <v>42.76</v>
+        <v>47.62</v>
       </c>
       <c r="X97" s="18" t="n">
-        <v>84.98999999999999</v>
+        <v>86.89</v>
       </c>
       <c r="Y97" s="18" t="n">
         <v>497.93</v>
       </c>
       <c r="Z97" s="37" t="n">
-        <v>738.87</v>
+        <v>745.63</v>
       </c>
       <c r="AA97" s="18" t="n">
-        <v>146.42</v>
+        <v>154.31</v>
       </c>
       <c r="AB97" s="19" t="n">
-        <v>38.01</v>
+        <v>181.55</v>
       </c>
       <c r="AC97" s="10" t="n"/>
       <c r="AD97" s="10" t="n"/>
@@ -18847,11 +18875,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>무형자산의증가</t>
         </is>
       </c>
       <c r="E98" s="18" t="n">
-        <v>31.93</v>
+        <v>0</v>
       </c>
       <c r="F98" s="9" t="n"/>
       <c r="G98" s="18" t="n">
@@ -18861,64 +18889,64 @@
         <v>0</v>
       </c>
       <c r="I98" s="18" t="n">
-        <v>115.01</v>
+        <v>0</v>
       </c>
       <c r="J98" s="18" t="n">
-        <v>71.09</v>
+        <v>186.1</v>
       </c>
       <c r="K98" s="37" t="n">
         <v>186.1</v>
       </c>
       <c r="L98" s="18" t="n">
-        <v>140.98</v>
+        <v>0</v>
       </c>
       <c r="M98" s="18" t="n">
-        <v>84.98</v>
+        <v>28.56</v>
       </c>
       <c r="N98" s="18" t="n">
-        <v>333.86</v>
+        <v>7</v>
       </c>
       <c r="O98" s="18" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="37" t="n">
-        <v>559.8200000000001</v>
+        <v>35.56</v>
       </c>
       <c r="Q98" s="18" t="n">
-        <v>103.39</v>
+        <v>7.03</v>
       </c>
       <c r="R98" s="18" t="n">
-        <v>68.15000000000001</v>
+        <v>0</v>
       </c>
       <c r="S98" s="18" t="n">
-        <v>76.8</v>
+        <v>0</v>
       </c>
       <c r="T98" s="18" t="n">
-        <v>153.62</v>
+        <v>0</v>
       </c>
       <c r="U98" s="37" t="n">
-        <v>401.96</v>
+        <v>7.03</v>
       </c>
       <c r="V98" s="18" t="n">
-        <v>113.19</v>
+        <v>0</v>
       </c>
       <c r="W98" s="18" t="n">
-        <v>47.62</v>
+        <v>4.86</v>
       </c>
       <c r="X98" s="18" t="n">
-        <v>86.89</v>
+        <v>1.9</v>
       </c>
       <c r="Y98" s="18" t="n">
-        <v>497.93</v>
+        <v>0</v>
       </c>
       <c r="Z98" s="37" t="n">
-        <v>745.63</v>
+        <v>6.76</v>
       </c>
       <c r="AA98" s="18" t="n">
-        <v>154.31</v>
+        <v>7.89</v>
       </c>
       <c r="AB98" s="19" t="n">
-        <v>181.55</v>
+        <v>143.54</v>
       </c>
       <c r="AC98" s="10" t="n"/>
       <c r="AD98" s="10" t="n"/>
@@ -18940,78 +18968,78 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
+          <t>재무활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E99" s="18" t="n">
-        <v>0</v>
+        <v>987.34</v>
       </c>
       <c r="F99" s="9" t="n"/>
       <c r="G99" s="18" t="n">
-        <v>0</v>
+        <v>368.12</v>
       </c>
       <c r="H99" s="18" t="n">
-        <v>0</v>
+        <v>-896.01</v>
       </c>
       <c r="I99" s="18" t="n">
-        <v>0</v>
+        <v>766.37</v>
       </c>
       <c r="J99" s="18" t="n">
-        <v>186.1</v>
+        <v>-2098.48</v>
       </c>
       <c r="K99" s="37" t="n">
-        <v>186.1</v>
+        <v>-1860</v>
       </c>
       <c r="L99" s="18" t="n">
-        <v>0</v>
+        <v>-675.13</v>
       </c>
       <c r="M99" s="18" t="n">
-        <v>28.56</v>
+        <v>-1078.06</v>
       </c>
       <c r="N99" s="18" t="n">
-        <v>7</v>
+        <v>462.88</v>
       </c>
       <c r="O99" s="18" t="n">
-        <v>0</v>
+        <v>7612.41</v>
       </c>
       <c r="P99" s="37" t="n">
-        <v>35.56</v>
+        <v>6322.1</v>
       </c>
       <c r="Q99" s="18" t="n">
-        <v>7.03</v>
+        <v>7368.43</v>
       </c>
       <c r="R99" s="18" t="n">
-        <v>0</v>
+        <v>1774.11</v>
       </c>
       <c r="S99" s="18" t="n">
-        <v>0</v>
+        <v>-274.73</v>
       </c>
       <c r="T99" s="18" t="n">
-        <v>0</v>
+        <v>4796.25</v>
       </c>
       <c r="U99" s="37" t="n">
-        <v>7.03</v>
+        <v>13664.06</v>
       </c>
       <c r="V99" s="18" t="n">
-        <v>0</v>
+        <v>371.83</v>
       </c>
       <c r="W99" s="18" t="n">
-        <v>4.86</v>
+        <v>740.96</v>
       </c>
       <c r="X99" s="18" t="n">
-        <v>1.9</v>
+        <v>-675.15</v>
       </c>
       <c r="Y99" s="18" t="n">
-        <v>0</v>
+        <v>1140.75</v>
       </c>
       <c r="Z99" s="37" t="n">
-        <v>6.76</v>
+        <v>1578.39</v>
       </c>
       <c r="AA99" s="18" t="n">
-        <v>7.89</v>
+        <v>2103.08</v>
       </c>
       <c r="AB99" s="19" t="n">
-        <v>143.54</v>
+        <v>-1011.22</v>
       </c>
       <c r="AC99" s="10" t="n"/>
       <c r="AD99" s="10" t="n"/>
@@ -19033,78 +19061,78 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>차입금의증가</t>
         </is>
       </c>
       <c r="E100" s="18" t="n">
-        <v>987.34</v>
+        <v>13319.53</v>
       </c>
       <c r="F100" s="9" t="n"/>
       <c r="G100" s="18" t="n">
-        <v>368.12</v>
+        <v>3076.73</v>
       </c>
       <c r="H100" s="18" t="n">
-        <v>-896.01</v>
+        <v>5262.22</v>
       </c>
       <c r="I100" s="18" t="n">
-        <v>766.37</v>
+        <v>4795.35</v>
       </c>
       <c r="J100" s="18" t="n">
-        <v>-2098.48</v>
+        <v>9761.99</v>
       </c>
       <c r="K100" s="37" t="n">
-        <v>-1860</v>
+        <v>22896.29</v>
       </c>
       <c r="L100" s="18" t="n">
-        <v>-675.13</v>
+        <v>4857.9</v>
       </c>
       <c r="M100" s="18" t="n">
-        <v>-1078.06</v>
+        <v>9017.889999999999</v>
       </c>
       <c r="N100" s="18" t="n">
-        <v>462.88</v>
+        <v>5959.07</v>
       </c>
       <c r="O100" s="18" t="n">
-        <v>7612.41</v>
+        <v>15328.77</v>
       </c>
       <c r="P100" s="37" t="n">
-        <v>6322.1</v>
+        <v>35163.63</v>
       </c>
       <c r="Q100" s="18" t="n">
-        <v>7368.43</v>
+        <v>3384.66</v>
       </c>
       <c r="R100" s="18" t="n">
-        <v>1774.11</v>
+        <v>4175.78</v>
       </c>
       <c r="S100" s="18" t="n">
-        <v>-274.73</v>
+        <v>3287.3</v>
       </c>
       <c r="T100" s="18" t="n">
-        <v>4796.25</v>
+        <v>5697.99</v>
       </c>
       <c r="U100" s="37" t="n">
-        <v>13664.06</v>
+        <v>16545.73</v>
       </c>
       <c r="V100" s="18" t="n">
-        <v>371.83</v>
+        <v>12615.32</v>
       </c>
       <c r="W100" s="18" t="n">
-        <v>740.96</v>
+        <v>6953.04</v>
       </c>
       <c r="X100" s="18" t="n">
-        <v>-675.15</v>
+        <v>5826.85</v>
       </c>
       <c r="Y100" s="18" t="n">
-        <v>1140.75</v>
+        <v>22486.54</v>
       </c>
       <c r="Z100" s="37" t="n">
-        <v>1578.39</v>
+        <v>47881.75</v>
       </c>
       <c r="AA100" s="18" t="n">
-        <v>2103.08</v>
+        <v>9610.82</v>
       </c>
       <c r="AB100" s="19" t="n">
-        <v>-1011.22</v>
+        <v>10978.74</v>
       </c>
       <c r="AC100" s="10" t="n"/>
       <c r="AD100" s="10" t="n"/>
@@ -19126,78 +19154,78 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>차입금의증가</t>
+          <t>차입금의감소</t>
         </is>
       </c>
       <c r="E101" s="18" t="n">
-        <v>13319.53</v>
+        <v>12302.26</v>
       </c>
       <c r="F101" s="9" t="n"/>
       <c r="G101" s="18" t="n">
-        <v>3076.73</v>
+        <v>2708.62</v>
       </c>
       <c r="H101" s="18" t="n">
-        <v>5262.22</v>
+        <v>6114.67</v>
       </c>
       <c r="I101" s="18" t="n">
-        <v>4795.35</v>
+        <v>4029.94</v>
       </c>
       <c r="J101" s="18" t="n">
-        <v>9761.99</v>
+        <v>11841.2</v>
       </c>
       <c r="K101" s="37" t="n">
-        <v>22896.29</v>
+        <v>24694.43</v>
       </c>
       <c r="L101" s="18" t="n">
-        <v>4857.9</v>
+        <v>5533.03</v>
       </c>
       <c r="M101" s="18" t="n">
-        <v>9017.889999999999</v>
+        <v>10108.95</v>
       </c>
       <c r="N101" s="18" t="n">
-        <v>5959.07</v>
+        <v>5475.05</v>
       </c>
       <c r="O101" s="18" t="n">
-        <v>15328.77</v>
+        <v>15849.05</v>
       </c>
       <c r="P101" s="37" t="n">
-        <v>35163.63</v>
+        <v>36966.08</v>
       </c>
       <c r="Q101" s="18" t="n">
-        <v>3384.66</v>
+        <v>7048.8</v>
       </c>
       <c r="R101" s="18" t="n">
-        <v>4175.78</v>
+        <v>2424.7</v>
       </c>
       <c r="S101" s="18" t="n">
-        <v>3287.3</v>
+        <v>3335.44</v>
       </c>
       <c r="T101" s="18" t="n">
-        <v>5697.99</v>
+        <v>930.73</v>
       </c>
       <c r="U101" s="37" t="n">
-        <v>16545.73</v>
+        <v>13739.67</v>
       </c>
       <c r="V101" s="18" t="n">
-        <v>12615.32</v>
+        <v>12272.05</v>
       </c>
       <c r="W101" s="18" t="n">
-        <v>6953.04</v>
+        <v>6172.82</v>
       </c>
       <c r="X101" s="18" t="n">
-        <v>5826.85</v>
+        <v>6546.13</v>
       </c>
       <c r="Y101" s="18" t="n">
-        <v>22486.54</v>
+        <v>21331.6</v>
       </c>
       <c r="Z101" s="37" t="n">
-        <v>47881.75</v>
+        <v>46322.6</v>
       </c>
       <c r="AA101" s="18" t="n">
-        <v>9610.82</v>
+        <v>4813.58</v>
       </c>
       <c r="AB101" s="19" t="n">
-        <v>10978.74</v>
+        <v>11982.99</v>
       </c>
       <c r="AC101" s="10" t="n"/>
       <c r="AD101" s="10" t="n"/>
@@ -19219,78 +19247,54 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>차입금의감소</t>
+          <t>리스부채의상환</t>
         </is>
       </c>
       <c r="E102" s="18" t="n">
-        <v>12302.26</v>
+        <v>29.94</v>
       </c>
       <c r="F102" s="9" t="n"/>
       <c r="G102" s="18" t="n">
-        <v>2708.62</v>
+        <v>0</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>6114.67</v>
+        <v>43.56</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>4029.94</v>
+        <v>-0.98</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>11841.2</v>
+        <v>19.28</v>
       </c>
       <c r="K102" s="37" t="n">
-        <v>24694.43</v>
+        <v>61.86</v>
       </c>
       <c r="L102" s="18" t="n">
-        <v>5533.03</v>
+        <v>0</v>
       </c>
       <c r="M102" s="18" t="n">
-        <v>10108.95</v>
-      </c>
-      <c r="N102" s="18" t="n">
-        <v>5475.05</v>
+        <v>23.74</v>
       </c>
       <c r="O102" s="18" t="n">
-        <v>15849.05</v>
-      </c>
-      <c r="P102" s="37" t="n">
-        <v>36966.08</v>
-      </c>
-      <c r="Q102" s="18" t="n">
-        <v>7048.8</v>
-      </c>
-      <c r="R102" s="18" t="n">
-        <v>2424.7</v>
-      </c>
-      <c r="S102" s="18" t="n">
-        <v>3335.44</v>
-      </c>
+        <v>47.87</v>
+      </c>
+      <c r="P102" s="9" t="n"/>
       <c r="T102" s="18" t="n">
-        <v>930.73</v>
-      </c>
-      <c r="U102" s="37" t="n">
-        <v>13739.67</v>
-      </c>
-      <c r="V102" s="18" t="n">
-        <v>12272.05</v>
-      </c>
-      <c r="W102" s="18" t="n">
-        <v>6172.82</v>
-      </c>
+        <v>37.77</v>
+      </c>
+      <c r="U102" s="9" t="n"/>
       <c r="X102" s="18" t="n">
-        <v>6546.13</v>
+        <v>0</v>
       </c>
       <c r="Y102" s="18" t="n">
-        <v>21331.6</v>
-      </c>
-      <c r="Z102" s="37" t="n">
-        <v>46322.6</v>
-      </c>
+        <v>38.28</v>
+      </c>
+      <c r="Z102" s="9" t="n"/>
       <c r="AA102" s="18" t="n">
-        <v>4813.58</v>
+        <v>8.85</v>
       </c>
       <c r="AB102" s="19" t="n">
-        <v>11982.99</v>
+        <v>36.6</v>
       </c>
       <c r="AC102" s="10" t="n"/>
       <c r="AD102" s="10" t="n"/>
@@ -19312,54 +19316,78 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>현금및현금성자산의증감</t>
         </is>
       </c>
       <c r="E103" s="18" t="n">
-        <v>29.94</v>
+        <v>3660.82</v>
       </c>
       <c r="F103" s="9" t="n"/>
       <c r="G103" s="18" t="n">
-        <v>0</v>
+        <v>-4702.15</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>43.56</v>
+        <v>-310.51</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>-0.98</v>
+        <v>1135.46</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>19.28</v>
+        <v>-146.57</v>
       </c>
       <c r="K103" s="37" t="n">
-        <v>61.86</v>
+        <v>-4023.77</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>0</v>
+        <v>1454.56</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>23.74</v>
+        <v>96.65000000000001</v>
+      </c>
+      <c r="N103" s="18" t="n">
+        <v>-314.98</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>47.87</v>
-      </c>
-      <c r="P103" s="9" t="n"/>
+        <v>3513.16</v>
+      </c>
+      <c r="P103" s="37" t="n">
+        <v>4749.39</v>
+      </c>
+      <c r="Q103" s="18" t="n">
+        <v>4628.68</v>
+      </c>
+      <c r="R103" s="18" t="n">
+        <v>-1723.39</v>
+      </c>
+      <c r="S103" s="18" t="n">
+        <v>-645.75</v>
+      </c>
       <c r="T103" s="18" t="n">
-        <v>37.77</v>
-      </c>
-      <c r="U103" s="9" t="n"/>
+        <v>4897.64</v>
+      </c>
+      <c r="U103" s="37" t="n">
+        <v>7157.18</v>
+      </c>
+      <c r="V103" s="18" t="n">
+        <v>-1422.06</v>
+      </c>
+      <c r="W103" s="18" t="n">
+        <v>-871.5700000000001</v>
+      </c>
       <c r="X103" s="18" t="n">
-        <v>0</v>
+        <v>4432.37</v>
       </c>
       <c r="Y103" s="18" t="n">
-        <v>38.28</v>
-      </c>
-      <c r="Z103" s="9" t="n"/>
+        <v>-6118.55</v>
+      </c>
+      <c r="Z103" s="37" t="n">
+        <v>-3979.81</v>
+      </c>
       <c r="AA103" s="18" t="n">
-        <v>8.85</v>
+        <v>1792.53</v>
       </c>
       <c r="AB103" s="19" t="n">
-        <v>36.6</v>
+        <v>2367.18</v>
       </c>
       <c r="AC103" s="10" t="n"/>
       <c r="AD103" s="10" t="n"/>
@@ -19381,7 +19409,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>기말현금및현금성자산</t>
         </is>
       </c>
       <c r="E104" s="18" t="n">
@@ -19389,22 +19417,22 @@
       </c>
       <c r="F104" s="9" t="n"/>
       <c r="G104" s="18" t="n">
-        <v>-4702.15</v>
+        <v>726.75</v>
       </c>
       <c r="H104" s="18" t="n">
-        <v>-310.51</v>
+        <v>-310.52</v>
       </c>
       <c r="I104" s="18" t="n">
-        <v>1135.46</v>
+        <v>1135.47</v>
       </c>
       <c r="J104" s="18" t="n">
         <v>-146.57</v>
       </c>
       <c r="K104" s="37" t="n">
-        <v>-4023.77</v>
+        <v>1405.13</v>
       </c>
       <c r="L104" s="18" t="n">
-        <v>1454.56</v>
+        <v>2859.69</v>
       </c>
       <c r="M104" s="18" t="n">
         <v>96.65000000000001</v>
@@ -19416,10 +19444,10 @@
         <v>3513.16</v>
       </c>
       <c r="P104" s="37" t="n">
-        <v>4749.39</v>
+        <v>6154.52</v>
       </c>
       <c r="Q104" s="18" t="n">
-        <v>4628.68</v>
+        <v>10783.2</v>
       </c>
       <c r="R104" s="18" t="n">
         <v>-1723.39</v>
@@ -19431,25 +19459,25 @@
         <v>4897.64</v>
       </c>
       <c r="U104" s="37" t="n">
-        <v>7157.18</v>
+        <v>13311.7</v>
       </c>
       <c r="V104" s="18" t="n">
-        <v>-1422.06</v>
+        <v>11889.63</v>
       </c>
       <c r="W104" s="18" t="n">
         <v>-871.5700000000001</v>
       </c>
       <c r="X104" s="18" t="n">
-        <v>4432.37</v>
+        <v>4432.38</v>
       </c>
       <c r="Y104" s="18" t="n">
-        <v>-6118.55</v>
+        <v>-6118.56</v>
       </c>
       <c r="Z104" s="37" t="n">
-        <v>-3979.81</v>
+        <v>9331.879999999999</v>
       </c>
       <c r="AA104" s="18" t="n">
-        <v>1792.53</v>
+        <v>11124.41</v>
       </c>
       <c r="AB104" s="19" t="n">
         <v>2367.18</v>
@@ -19474,79 +19502,21 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
-        </is>
-      </c>
-      <c r="E105" s="18" t="n">
-        <v>3660.82</v>
+          <t>무형자산의감소</t>
+        </is>
       </c>
       <c r="F105" s="9" t="n"/>
-      <c r="G105" s="18" t="n">
-        <v>726.75</v>
-      </c>
-      <c r="H105" s="18" t="n">
-        <v>-310.52</v>
-      </c>
       <c r="I105" s="18" t="n">
-        <v>1135.47</v>
-      </c>
-      <c r="J105" s="18" t="n">
-        <v>-146.57</v>
-      </c>
-      <c r="K105" s="37" t="n">
-        <v>1405.13</v>
-      </c>
-      <c r="L105" s="18" t="n">
-        <v>2859.69</v>
-      </c>
-      <c r="M105" s="18" t="n">
-        <v>96.65000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K105" s="9" t="n"/>
       <c r="N105" s="18" t="n">
-        <v>-314.98</v>
-      </c>
-      <c r="O105" s="18" t="n">
-        <v>3513.16</v>
-      </c>
-      <c r="P105" s="37" t="n">
-        <v>6154.52</v>
-      </c>
-      <c r="Q105" s="18" t="n">
-        <v>10783.2</v>
-      </c>
-      <c r="R105" s="18" t="n">
-        <v>-1723.39</v>
-      </c>
-      <c r="S105" s="18" t="n">
-        <v>-645.75</v>
-      </c>
-      <c r="T105" s="18" t="n">
-        <v>4897.64</v>
-      </c>
-      <c r="U105" s="37" t="n">
-        <v>13311.7</v>
-      </c>
-      <c r="V105" s="18" t="n">
-        <v>11889.63</v>
-      </c>
-      <c r="W105" s="18" t="n">
-        <v>-871.5700000000001</v>
-      </c>
-      <c r="X105" s="18" t="n">
-        <v>4432.38</v>
-      </c>
-      <c r="Y105" s="18" t="n">
-        <v>-6118.56</v>
-      </c>
-      <c r="Z105" s="37" t="n">
-        <v>9331.879999999999</v>
-      </c>
-      <c r="AA105" s="18" t="n">
-        <v>11124.41</v>
-      </c>
-      <c r="AB105" s="19" t="n">
-        <v>2367.18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P105" s="9" t="n"/>
+      <c r="U105" s="9" t="n"/>
+      <c r="Z105" s="9" t="n"/>
+      <c r="AB105" s="5" t="n"/>
       <c r="AC105" s="10" t="n"/>
       <c r="AD105" s="10" t="n"/>
       <c r="AE105" s="11" t="n"/>
@@ -19567,21 +19537,51 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="F106" s="9" t="n"/>
-      <c r="I106" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="K106" s="9" t="n"/>
-      <c r="N106" s="18" t="n">
-        <v>0</v>
+      <c r="O106" s="18" t="n">
+        <v>26.06</v>
       </c>
       <c r="P106" s="9" t="n"/>
-      <c r="U106" s="9" t="n"/>
-      <c r="Z106" s="9" t="n"/>
-      <c r="AB106" s="5" t="n"/>
+      <c r="Q106" s="18" t="n">
+        <v>-82.92</v>
+      </c>
+      <c r="R106" s="18" t="n">
+        <v>115.91</v>
+      </c>
+      <c r="S106" s="18" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="T106" s="18" t="n">
+        <v>72.89</v>
+      </c>
+      <c r="U106" s="37" t="n">
+        <v>123.42</v>
+      </c>
+      <c r="V106" s="18" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="W106" s="18" t="n">
+        <v>37.21</v>
+      </c>
+      <c r="X106" s="18" t="n">
+        <v>228.3</v>
+      </c>
+      <c r="Y106" s="18" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="Z106" s="37" t="n">
+        <v>275.77</v>
+      </c>
+      <c r="AA106" s="18" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="AB106" s="19" t="n">
+        <v>30.85</v>
+      </c>
       <c r="AC106" s="10" t="n"/>
       <c r="AD106" s="10" t="n"/>
       <c r="AE106" s="11" t="n"/>
@@ -19595,71 +19595,6 @@
       <c r="AM106" s="10" t="n"/>
       <c r="AN106" s="10" t="n"/>
       <c r="AO106" s="11" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>1</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>이자수취(CF)</t>
-        </is>
-      </c>
-      <c r="F107" s="9" t="n"/>
-      <c r="K107" s="9" t="n"/>
-      <c r="O107" s="18" t="n">
-        <v>26.06</v>
-      </c>
-      <c r="P107" s="9" t="n"/>
-      <c r="Q107" s="18" t="n">
-        <v>-82.92</v>
-      </c>
-      <c r="R107" s="18" t="n">
-        <v>115.91</v>
-      </c>
-      <c r="S107" s="18" t="n">
-        <v>17.54</v>
-      </c>
-      <c r="T107" s="18" t="n">
-        <v>72.89</v>
-      </c>
-      <c r="U107" s="37" t="n">
-        <v>123.42</v>
-      </c>
-      <c r="V107" s="18" t="n">
-        <v>12.94</v>
-      </c>
-      <c r="W107" s="18" t="n">
-        <v>37.21</v>
-      </c>
-      <c r="X107" s="18" t="n">
-        <v>228.3</v>
-      </c>
-      <c r="Y107" s="18" t="n">
-        <v>-2.68</v>
-      </c>
-      <c r="Z107" s="37" t="n">
-        <v>275.77</v>
-      </c>
-      <c r="AA107" s="18" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="AB107" s="19" t="n">
-        <v>30.85</v>
-      </c>
-      <c r="AC107" s="10" t="n"/>
-      <c r="AD107" s="10" t="n"/>
-      <c r="AE107" s="11" t="n"/>
-      <c r="AF107" s="10" t="n"/>
-      <c r="AG107" s="10" t="n"/>
-      <c r="AH107" s="10" t="n"/>
-      <c r="AI107" s="10" t="n"/>
-      <c r="AJ107" s="11" t="n"/>
-      <c r="AK107" s="10" t="n"/>
-      <c r="AL107" s="10" t="n"/>
-      <c r="AM107" s="10" t="n"/>
-      <c r="AN107" s="10" t="n"/>
-      <c r="AO107" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19920,7 +19855,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32984,69 +32919,69 @@
           <t>유통주식수</t>
         </is>
       </c>
-      <c r="E33" s="27" t="n">
-        <v>159.155</v>
+      <c r="E33" s="33" t="n">
+        <v>31.8310558</v>
       </c>
       <c r="F33" s="28">
         <f>E33</f>
         <v/>
       </c>
-      <c r="G33" s="27" t="n">
-        <v>159.155</v>
-      </c>
-      <c r="H33" s="27" t="n">
-        <v>159.155</v>
-      </c>
-      <c r="I33" s="27" t="n">
-        <v>159.155</v>
-      </c>
-      <c r="J33" s="27" t="n">
-        <v>159.155</v>
+      <c r="G33" s="33" t="n">
+        <v>31.8310558</v>
+      </c>
+      <c r="H33" s="33" t="n">
+        <v>31.8310558</v>
+      </c>
+      <c r="I33" s="33" t="n">
+        <v>31.8310558</v>
+      </c>
+      <c r="J33" s="33" t="n">
+        <v>31.8310558</v>
       </c>
       <c r="K33" s="28">
         <f>J33</f>
         <v/>
       </c>
-      <c r="L33" s="27" t="n">
-        <v>159.155</v>
-      </c>
-      <c r="M33" s="27" t="n">
-        <v>159.155</v>
-      </c>
-      <c r="N33" s="27" t="n">
-        <v>159.155</v>
-      </c>
-      <c r="O33" s="27" t="n">
-        <v>159.155</v>
+      <c r="L33" s="33" t="n">
+        <v>31.8310558</v>
+      </c>
+      <c r="M33" s="33" t="n">
+        <v>31.8310558</v>
+      </c>
+      <c r="N33" s="33" t="n">
+        <v>31.8310558</v>
+      </c>
+      <c r="O33" s="33" t="n">
+        <v>31.8310558</v>
       </c>
       <c r="P33" s="28">
         <f>O33</f>
         <v/>
       </c>
-      <c r="Q33" s="27" t="n">
-        <v>159.155</v>
-      </c>
-      <c r="R33" s="27" t="n">
-        <v>159.155</v>
-      </c>
-      <c r="S33" s="27" t="n">
-        <v>159.155</v>
-      </c>
-      <c r="T33" s="27" t="n">
-        <v>159.155</v>
+      <c r="Q33" s="33" t="n">
+        <v>31.8310558</v>
+      </c>
+      <c r="R33" s="33" t="n">
+        <v>31.8310558</v>
+      </c>
+      <c r="S33" s="33" t="n">
+        <v>31.8310558</v>
+      </c>
+      <c r="T33" s="33" t="n">
+        <v>31.8310558</v>
       </c>
       <c r="U33" s="28">
         <f>T33</f>
         <v/>
       </c>
-      <c r="V33" s="27" t="n">
-        <v>159.155</v>
-      </c>
-      <c r="W33" s="27" t="n">
-        <v>175.566</v>
-      </c>
-      <c r="X33" s="27" t="n">
-        <v>179.668</v>
+      <c r="V33" s="33" t="n">
+        <v>31.8310558</v>
+      </c>
+      <c r="W33" s="33" t="n">
+        <v>35.113107</v>
+      </c>
+      <c r="X33" s="33" t="n">
+        <v>35.9336162</v>
       </c>
       <c r="Y33" s="27" t="n">
         <v>35.93</v>
@@ -42459,7 +42394,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-76</v>
+        <v>-75.8</v>
       </c>
     </row>
     <row r="30">
@@ -42496,7 +42431,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-0.0862</v>
+        <v>-0.08599999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -42520,7 +42455,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>109.85</v>
+        <v>109.75</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/096350_model.xlsx
+++ b/argus/kship/models/096350_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 192996억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 192994억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 201022억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 201042억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 207864억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 207907억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 215622억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 215687억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 226082억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 226171억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 238445억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 238531억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 252123억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 252204억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 266563억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 266640억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 279067억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 279138억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 192996억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 192994억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 201022억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 201042억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 207864억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 207907억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 215622억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 215687억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 226082억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 226171억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 238445억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 238531억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 252123억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 252204억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 266563억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 266640억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 279067억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 279138억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -5310,35 +5310,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5667,35 +5667,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5786,35 +5786,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5905,35 +5905,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6024,35 +6024,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6143,35 +6143,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6278,7 +6278,7 @@
         <v>1859</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1877</v>
+        <v>1887</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6551,7 +6551,7 @@
         <v>1800.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1890.8</v>
+        <v>1892.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6710,29 +6710,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.0456225</v>
+        <v>0.045716628</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.201002442</v>
+        <v>0.201267189</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.185133036</v>
+        <v>0.185472907</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.171427407</v>
+        <v>0.171916385</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.186163748</v>
+        <v>0.186462037</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.212944185</v>
+        <v>0.213073566</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.236265312</v>
+        <v>0.236238532</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.234381522</v>
+        <v>0.234179416</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7024,32 +7024,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.001215286</v>
+        <v>0.001215176</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.001234459</v>
+        <v>0.001234187</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.001229055</v>
+        <v>0.001228702</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.001217476</v>
+        <v>0.001216968</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.001214283</v>
+        <v>0.001213868</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.001235824</v>
+        <v>0.00123542</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.00122614</v>
+        <v>0.001225815</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.001211745</v>
+        <v>0.001211438</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8381,29 +8381,29 @@
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.009884656</v>
+        <v>-0.009884791</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.010116382</v>
+        <v>0.010116396</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>8.4008e-05</v>
+        <v>8.3853e-05</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>5.1556e-05</v>
+        <v>5.1552e-05</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.000119802</v>
+        <v>0.000119686</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>2.0174e-05</v>
+        <v>2.0213e-05</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.009920754</v>
+        <v>0.009920745999999999</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.000145395</v>
+        <v>-0.010145307</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8509,29 +8509,29 @@
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.000115344</v>
+        <v>0.000115209</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.000116382</v>
+        <v>0.000116396</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>8.4008e-05</v>
+        <v>8.3853e-05</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>5.1556e-05</v>
+        <v>5.1552e-05</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.000119802</v>
+        <v>0.000119686</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>0.010020174</v>
+        <v>0.010020213</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-7.924600000000001e-05</v>
+        <v>-7.9254e-05</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.000145395</v>
+        <v>-0.000145307</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -9578,11 +9578,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>1877</v>
+        <v>1887</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,908원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,890원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.129670371498173</v>
+        <v>0.1296707143971596</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.01342205540426584</v>
+        <v>0.01342205540426368</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04177651543000203</v>
+        <v>0.04177651543000138</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="33">
@@ -42455,7 +42455,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>109.75</v>
+        <v>110.07</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/096350_model.xlsx
+++ b/argus/kship/models/096350_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 192994억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 192991억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 201042억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 201030억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 207907억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 207885억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 215687억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 215656억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 226171억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 226135억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 238531억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 238496억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 252204억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 252171억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 266640억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 266609억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 279138억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 279109억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 192994억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 192991억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 201042억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 201030억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 207907억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 207885억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 215687억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 215656억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 226171억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 226135억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 238531억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 238496억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 252204억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 252171억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 266640억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 266609억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 279138억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 279109억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4439,7 +4439,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5667,35 +5667,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5786,35 +5786,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5905,35 +5905,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6024,35 +6024,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6143,35 +6143,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6706,33 +6706,33 @@
         <v>0.200541631</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.380793795</v>
+        <v>0.38073753</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.045716628</v>
+        <v>0.0456225</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.201267189</v>
+        <v>0.201108341</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.185472907</v>
+        <v>0.185327248</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.171916385</v>
+        <v>0.171760391</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.186462037</v>
+        <v>0.186388801</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.213073566</v>
+        <v>0.213057662</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.236238532</v>
+        <v>0.236267562</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.234179416</v>
+        <v>0.234254912</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7017,39 +7017,39 @@
         <v>0.001213828</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.001222444</v>
+        <v>0.001222494</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.001215176</v>
+        <v>0.001215286</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.001234187</v>
+        <v>0.00123435</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.001228702</v>
+        <v>0.001228853</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.001216968</v>
+        <v>0.00121718</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.001213868</v>
+        <v>0.001214053</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.00123542</v>
+        <v>0.0012356</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.001225815</v>
+        <v>0.001225937</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.001211438</v>
+        <v>0.001211575</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8377,33 +8377,33 @@
         <v>0.003104454</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-8.7233e-05</v>
+        <v>-8.7187e-05</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.009884791</v>
+        <v>-0.009884656</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.010116396</v>
+        <v>0.010116345</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>8.3853e-05</v>
+        <v>8.3856e-05</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>5.1552e-05</v>
+        <v>5.1664e-05</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.000119686</v>
+        <v>0.000119893</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>2.0213e-05</v>
+        <v>2.0327e-05</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.009920745999999999</v>
+        <v>0.009920793000000001</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.010145307</v>
+        <v>-0.010145142</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8505,33 +8505,33 @@
         <v>0.000504454</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-8.7233e-05</v>
+        <v>-8.7187e-05</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.000115209</v>
+        <v>0.000115344</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.000116396</v>
+        <v>0.000116345</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>8.3853e-05</v>
+        <v>8.3856e-05</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>5.1552e-05</v>
+        <v>5.1664e-05</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.000119686</v>
+        <v>0.000119893</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>0.010020213</v>
+        <v>0.010020327</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-7.9254e-05</v>
+        <v>-7.9207e-05</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.000145307</v>
+        <v>-0.000145142</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1296707143971596</v>
+        <v>0.1296774144440385</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/096350_model.xlsx
+++ b/argus/kship/models/096350_model.xlsx
@@ -4439,7 +4439,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/096350_model.xlsx
+++ b/argus/kship/models/096350_model.xlsx
@@ -4439,7 +4439,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
         <v>1859</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1887</v>
+        <v>1790</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6460,7 +6460,7 @@
         <v>1348</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>1820</v>
+        <v>1730</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6551,7 +6551,7 @@
         <v>1800.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1892.8</v>
+        <v>1875.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>1887</v>
+        <v>1790</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34797,7 +34797,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40186,7 +40186,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42421,7 +42421,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="33">
@@ -42455,7 +42455,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>110.07</v>
+        <v>106.99</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/096350_model.xlsx
+++ b/argus/kship/models/096350_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 192991억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 192984억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 201030억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 200982억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 207885억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 207797억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 215656억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 215525억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 226135억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 225970억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 238496억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 238333억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 252171억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 252014억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 266609억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 266459억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 279109억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 278971억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 192991억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 192984억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 201030억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 200982억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 207885억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 207797억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 215656억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 215525억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 226135억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 225970억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 238496억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 238333억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 252171억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 252014억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 266609억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 266459억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 279109억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 278971억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4439,7 +4439,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5667,35 +5667,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5786,35 +5786,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5905,35 +5905,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6024,35 +6024,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6143,35 +6143,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6278,7 +6278,7 @@
         <v>1859</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1790</v>
+        <v>1772</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6460,7 +6460,7 @@
         <v>1348</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>1730</v>
+        <v>1683</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6551,7 +6551,7 @@
         <v>1800.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1875.7</v>
+        <v>1860.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6710,29 +6710,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.0456225</v>
+        <v>0.04538718</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.201108341</v>
+        <v>0.200631794</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.185327248</v>
+        <v>0.184598951</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.171760391</v>
+        <v>0.170904645</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.186388801</v>
+        <v>0.185845489</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.213057662</v>
+        <v>0.212789416</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.236267562</v>
+        <v>0.236330847</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.234254912</v>
+        <v>0.234565323</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7024,32 +7024,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.001215286</v>
+        <v>0.001215559</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.00123435</v>
+        <v>0.00123484</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.001228853</v>
+        <v>0.001229609</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.00121718</v>
+        <v>0.001218069</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.001214053</v>
+        <v>0.001214882</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.0012356</v>
+        <v>0.001236364</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.001225937</v>
+        <v>0.001226628</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.001211575</v>
+        <v>0.001212155</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8381,29 +8381,29 @@
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.009884656</v>
+        <v>-0.009884782</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.010116345</v>
+        <v>0.010116361</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>8.3856e-05</v>
+        <v>8.3977e-05</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>5.1664e-05</v>
+        <v>5.1502e-05</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.000119893</v>
+        <v>0.000119722</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>2.0327e-05</v>
+        <v>2.0375e-05</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.009920793000000001</v>
+        <v>0.009920817</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.010145142</v>
+        <v>-0.000145361</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8509,29 +8509,29 @@
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.000115344</v>
+        <v>0.000115218</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.000116345</v>
+        <v>0.000116361</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>8.3856e-05</v>
+        <v>8.3977e-05</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>5.1664e-05</v>
+        <v>5.1502e-05</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.000119893</v>
+        <v>0.000119722</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>0.010020327</v>
+        <v>0.010020375</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-7.9207e-05</v>
+        <v>-7.9183e-05</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.000145142</v>
+        <v>-0.000145361</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8765,10 +8765,10 @@
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.010299998</v>
+        <v>0.010317309</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.010246393</v>
+        <v>0.010229083</v>
       </c>
       <c r="AH35" s="24" t="n">
         <v>0.010125509</v>
@@ -8784,10 +8784,10 @@
         <v>0.009860245</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.009747669</v>
+        <v>0.009763969000000001</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.009588997</v>
+        <v>0.009572699</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9578,11 +9578,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>1790</v>
+        <v>1772</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,890원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,860원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1296774144440385</v>
+        <v>0.1296714426595287</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34797,7 +34797,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40186,7 +40186,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42421,7 +42421,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="33">
@@ -42455,7 +42455,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>106.99</v>
+        <v>106.42</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/096350_model.xlsx
+++ b/argus/kship/models/096350_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 192984억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 192982억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 200982억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 201021억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 207797억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 207875억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 215525억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 215643억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 225970억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 226126억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 238333억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 238483억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 252014억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 252156억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 266459억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 266594억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 278971억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 279095억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 192984억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 192982억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 200982억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 201021억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 207797억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 207875억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 215525억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 215643억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 225970억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 226126억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 238333억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 238483억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 252014억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 252156억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 266459억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 266594억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 278971억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 279095억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4439,7 +4439,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5667,35 +5667,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5786,35 +5786,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5905,35 +5905,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6024,35 +6024,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6143,35 +6143,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6278,7 +6278,7 @@
         <v>1859</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1772</v>
+        <v>1756</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6551,7 +6551,7 @@
         <v>1800.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1860.7</v>
+        <v>1845.6</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6706,33 +6706,33 @@
         <v>0.200541631</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.38073753</v>
+        <v>0.380681265</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.04538718</v>
+        <v>0.0456225</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.200631794</v>
+        <v>0.201055391</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.184598951</v>
+        <v>0.185230142</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.170904645</v>
+        <v>0.171767391</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.185845489</v>
+        <v>0.186343791</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.212789416</v>
+        <v>0.213022969</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.236330847</v>
+        <v>0.23628692</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.234565323</v>
+        <v>0.234228281</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7017,39 +7017,39 @@
         <v>0.001213828</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.001222494</v>
+        <v>0.001222544</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.001215559</v>
+        <v>0.001215286</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.00123484</v>
+        <v>0.001234405</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.001229609</v>
+        <v>0.001228954</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.001218069</v>
+        <v>0.001217222</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.001214882</v>
+        <v>0.001214099</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.001236364</v>
+        <v>0.00123569</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.001226628</v>
+        <v>0.001226018</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.001212155</v>
+        <v>0.001211643</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8377,33 +8377,33 @@
         <v>0.003104454</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-8.7187e-05</v>
+        <v>-8.7143e-05</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.009884782</v>
+        <v>-0.009884656</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.010116361</v>
+        <v>0.010116477</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>8.3977e-05</v>
+        <v>8.3935e-05</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>5.1502e-05</v>
+        <v>5.1569e-05</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.000119722</v>
+        <v>0.000119876</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>2.0375e-05</v>
+        <v>2.0379e-05</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.009920817</v>
+        <v>0.009920719999999999</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.000145361</v>
+        <v>-0.010145242</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8505,33 +8505,33 @@
         <v>0.000504454</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-8.7187e-05</v>
+        <v>-8.7143e-05</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.000115218</v>
+        <v>0.000115344</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.000116361</v>
+        <v>0.000116477</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>8.3977e-05</v>
+        <v>8.3935e-05</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>5.1502e-05</v>
+        <v>5.1569e-05</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.000119722</v>
+        <v>0.000119876</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>0.010020375</v>
+        <v>0.010020379</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-7.9183e-05</v>
+        <v>-7.928e-05</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.000145361</v>
+        <v>-0.000145242</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8765,10 +8765,10 @@
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.010317309</v>
+        <v>0.010299998</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.010229083</v>
+        <v>0.010246393</v>
       </c>
       <c r="AH35" s="24" t="n">
         <v>0.010125509</v>
@@ -8784,10 +8784,10 @@
         <v>0.009860245</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.009763969000000001</v>
+        <v>0.009747669</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.009572699</v>
+        <v>0.009588997</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9578,11 +9578,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>1772</v>
+        <v>1756</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,860원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,782원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1296714426595287</v>
+        <v>0.1296719190073837</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34797,7 +34797,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40186,7 +40186,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42421,7 +42421,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="33">
@@ -42455,7 +42455,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>106.42</v>
+        <v>105.91</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/096350_model.xlsx
+++ b/argus/kship/models/096350_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 192982억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 193158억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 201021억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 201294억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 207875억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 208134억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 215643억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 215801억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 226126억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 225943억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 238483억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 237998억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 252156억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 251465억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 266594억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 265794억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 279095억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 278287억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 192982억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 193158억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 201021억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 201294억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 207875억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 208134억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 215643억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 215801억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 226126억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 225943억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 238483억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 237998억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 252156억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 251465억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 266594억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 265794억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 279095억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 278287억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4439,7 +4439,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5667,35 +5667,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5786,35 +5786,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5905,35 +5905,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6024,35 +6024,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6143,35 +6143,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6278,7 +6278,7 @@
         <v>1859</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1756</v>
+        <v>1772</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6460,7 +6460,7 @@
         <v>1348</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>1683</v>
+        <v>1562</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6551,7 +6551,7 @@
         <v>1800.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1845.6</v>
+        <v>1808.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6706,33 +6706,33 @@
         <v>0.200541631</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.380681265</v>
+        <v>0.381975355</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.0456225</v>
+        <v>0.047034422</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.201055391</v>
+        <v>0.202590929</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.185230142</v>
+        <v>0.186104098</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.171767391</v>
+        <v>0.169733735</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.186343791</v>
+        <v>0.182316717</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.213022969</v>
+        <v>0.208171892</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.23628692</v>
+        <v>0.231691842</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.234228281</v>
+        <v>0.231666145</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7017,39 +7017,39 @@
         <v>0.001213828</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.001222544</v>
+        <v>0.001221399</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.001215286</v>
+        <v>0.001213647</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.001234405</v>
+        <v>0.001232828</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.001228954</v>
+        <v>0.001228049</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.001217222</v>
+        <v>0.001218196</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.001214099</v>
+        <v>0.001216591</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.00123569</v>
+        <v>0.001239067</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.001226018</v>
+        <v>0.001229685</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.001211643</v>
+        <v>0.001215136</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8377,33 +8377,33 @@
         <v>0.003104454</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-8.7143e-05</v>
+        <v>-8.7193e-05</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.009884656</v>
+        <v>-0.009884698000000001</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.010116477</v>
+        <v>0.010116286</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>8.3935e-05</v>
+        <v>8.4064e-05</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>5.1569e-05</v>
+        <v>5.1448e-05</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.000119876</v>
+        <v>0.000119734</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>2.0379e-05</v>
+        <v>2.026e-05</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.009920719999999999</v>
+        <v>0.009920666999999999</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.010145242</v>
+        <v>-0.000145049</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8505,33 +8505,33 @@
         <v>0.000504454</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-8.7143e-05</v>
+        <v>-8.7193e-05</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.000115344</v>
+        <v>0.000115302</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.000116477</v>
+        <v>0.000116286</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>8.3935e-05</v>
+        <v>8.4064e-05</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>5.1569e-05</v>
+        <v>5.1448e-05</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.000119876</v>
+        <v>0.000119734</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>0.010020379</v>
+        <v>0.01002026</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-7.928e-05</v>
+        <v>-7.933299999999999e-05</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.000145242</v>
+        <v>-0.000145049</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8784,10 +8784,10 @@
         <v>0.009860245</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.009747669</v>
+        <v>0.009763969000000001</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.009588997</v>
+        <v>0.009572699</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9578,11 +9578,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>1756</v>
+        <v>1772</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,782원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,648원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1296719190073837</v>
+        <v>0.1296781665244423</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34797,7 +34797,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40186,7 +40186,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42421,7 +42421,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="33">
@@ -42455,7 +42455,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>105.91</v>
+        <v>106.42</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/096350_model.xlsx
+++ b/argus/kship/models/096350_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 193158억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 193286억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 201294억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 201520억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 208134억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 208372억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 215801억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 215985억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 225943억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 225896억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 237998억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 237721억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 251465억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 251030억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 265794억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 265277억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 278287억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 277763억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 193158억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 193286억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 201294억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 201520억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 208134억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 208372억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 215801억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 215985억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 225943억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 225896억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 237998억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 237721억 × 비례계수 0.0046 × 계절비중 Q1 0.240(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 251465억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 251030억 × 비례계수 0.0046 × 계절비중 Q2 0.237(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 265794억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 265277억 × 비례계수 0.0046 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 278287억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 277763억 × 비례계수 0.0046 × 계절비중 Q4 0.276(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.83, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4439,7 +4439,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5667,35 +5667,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5786,35 +5786,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5905,35 +5905,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6024,35 +6024,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6143,35 +6143,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6278,7 +6278,7 @@
         <v>1859</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1772</v>
+        <v>1521</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6460,7 +6460,7 @@
         <v>1348</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>1562</v>
+        <v>1521</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6551,7 +6551,7 @@
         <v>1800.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1808.2</v>
+        <v>1764.6</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6706,33 +6706,33 @@
         <v>0.200541631</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.381975355</v>
+        <v>0.382875591</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.047034422</v>
+        <v>0.048211024</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.202590929</v>
+        <v>0.203967618</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.186104098</v>
+        <v>0.187123713</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.169733735</v>
+        <v>0.168728131</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.182316717</v>
+        <v>0.179597701</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.208171892</v>
+        <v>0.204679391</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.231691842</v>
+        <v>0.228220859</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.231666145</v>
+        <v>0.229590949</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7017,39 +7017,39 @@
         <v>0.001213828</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.001221399</v>
+        <v>0.001220604</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.001213647</v>
+        <v>0.001212284</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.001232828</v>
+        <v>0.001231419</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.001228049</v>
+        <v>0.001226994</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.001218196</v>
+        <v>0.001218451</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.001216591</v>
+        <v>0.001218027</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.001239067</v>
+        <v>0.001204731</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.001229685</v>
+        <v>0.001232101</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.001215136</v>
+        <v>0.001217441</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8377,33 +8377,33 @@
         <v>0.003104454</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-8.7193e-05</v>
+        <v>-0.010087164</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.009884698000000001</v>
+        <v>0.000115146</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.010116286</v>
+        <v>0.010116443</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>8.4064e-05</v>
+        <v>8.400599999999999e-05</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>5.1448e-05</v>
+        <v>5.1606e-05</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.000119734</v>
+        <v>0.000119856</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>2.026e-05</v>
+        <v>-0.00997981</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.009920666999999999</v>
+        <v>0.009920678</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.000145049</v>
+        <v>-0.000145064</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8505,33 +8505,33 @@
         <v>0.000504454</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-8.7193e-05</v>
+        <v>-8.716399999999999e-05</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.000115302</v>
+        <v>0.000115146</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.000116286</v>
+        <v>0.000116443</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>8.4064e-05</v>
+        <v>8.400599999999999e-05</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>5.1448e-05</v>
+        <v>5.1606e-05</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.000119734</v>
+        <v>0.000119856</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>0.01002026</v>
+        <v>2.019e-05</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-7.933299999999999e-05</v>
+        <v>-7.9322e-05</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.000145049</v>
+        <v>-0.000145064</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8768,13 +8768,13 @@
         <v>0.010299998</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.010246393</v>
+        <v>0.010229259</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.010125509</v>
+        <v>0.010125681</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.009956848000000001</v>
+        <v>0.009973806</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
@@ -8787,7 +8787,7 @@
         <v>0.009763969000000001</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.009572699</v>
+        <v>0.009588842</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9578,11 +9578,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>1772</v>
+        <v>1521</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,648원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,692원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1296781665244423</v>
+        <v>0.1296741661680127</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34797,7 +34797,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40186,7 +40186,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42421,7 +42421,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="33">
@@ -42455,7 +42455,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>106.42</v>
+        <v>98.43000000000001</v>
       </c>
     </row>
     <row r="37">
